--- a/AAII_Financials/Quarterly/QSG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QSG_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
   <si>
     <t>QSG</t>
   </si>
@@ -656,174 +656,199 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>114400</v>
+        <v>136300</v>
       </c>
       <c r="E8" s="3">
-        <v>111500</v>
+        <v>120800</v>
       </c>
       <c r="F8" s="3">
-        <v>108600</v>
+        <v>115200</v>
       </c>
       <c r="G8" s="3">
-        <v>91000</v>
+        <v>112200</v>
       </c>
       <c r="H8" s="3">
-        <v>86900</v>
+        <v>109300</v>
       </c>
       <c r="I8" s="3">
+        <v>91700</v>
+      </c>
+      <c r="J8" s="3">
+        <v>87400</v>
+      </c>
+      <c r="K8" s="3">
         <v>95400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>111000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>102500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>86000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>81200</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>16000</v>
+        <v>20200</v>
       </c>
       <c r="E9" s="3">
+        <v>16400</v>
+      </c>
+      <c r="F9" s="3">
+        <v>16100</v>
+      </c>
+      <c r="G9" s="3">
         <v>14000</v>
       </c>
-      <c r="F9" s="3">
-        <v>13700</v>
-      </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
+        <v>13800</v>
+      </c>
+      <c r="I9" s="3">
         <v>10400</v>
       </c>
-      <c r="H9" s="3">
-        <v>14900</v>
-      </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
+        <v>15000</v>
+      </c>
+      <c r="K9" s="3">
         <v>31600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>27900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>11900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>10500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>7600</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>98300</v>
+        <v>116100</v>
       </c>
       <c r="E10" s="3">
-        <v>97500</v>
+        <v>104400</v>
       </c>
       <c r="F10" s="3">
-        <v>94900</v>
+        <v>99000</v>
       </c>
       <c r="G10" s="3">
-        <v>80700</v>
+        <v>98200</v>
       </c>
       <c r="H10" s="3">
-        <v>72000</v>
+        <v>95500</v>
       </c>
       <c r="I10" s="3">
+        <v>81200</v>
+      </c>
+      <c r="J10" s="3">
+        <v>72500</v>
+      </c>
+      <c r="K10" s="3">
         <v>63800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>83200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>90600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>75600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>73600</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -837,43 +862,51 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>7400</v>
+        <v>5700</v>
       </c>
       <c r="E12" s="3">
-        <v>6800</v>
+        <v>6100</v>
       </c>
       <c r="F12" s="3">
+        <v>7500</v>
+      </c>
+      <c r="G12" s="3">
+        <v>6900</v>
+      </c>
+      <c r="H12" s="3">
         <v>8900</v>
       </c>
-      <c r="G12" s="3">
-        <v>7200</v>
-      </c>
-      <c r="H12" s="3">
-        <v>18300</v>
-      </c>
       <c r="I12" s="3">
+        <v>7300</v>
+      </c>
+      <c r="J12" s="3">
+        <v>18400</v>
+      </c>
+      <c r="K12" s="3">
         <v>13100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>14200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>5800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>10700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -907,8 +940,14 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -942,8 +981,14 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -977,8 +1022,14 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -989,78 +1040,92 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>107800</v>
+        <v>122100</v>
       </c>
       <c r="E17" s="3">
         <v>114700</v>
       </c>
       <c r="F17" s="3">
-        <v>114700</v>
+        <v>108500</v>
       </c>
       <c r="G17" s="3">
-        <v>104000</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>12</v>
+        <v>115400</v>
+      </c>
+      <c r="H17" s="3">
+        <v>115500</v>
       </c>
       <c r="I17" s="3">
+        <v>104700</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K17" s="3">
         <v>95200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>103700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>114200</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>6100</v>
+      </c>
+      <c r="F18" s="3">
         <v>6600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-3200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-6200</v>
       </c>
-      <c r="G18" s="3">
-        <v>-12900</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="I18" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K18" s="3">
         <v>200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>7300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-11700</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1074,43 +1139,51 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>600</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F20" s="3">
         <v>1200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>1000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>600</v>
-      </c>
-      <c r="G20" s="3">
-        <v>900</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>12</v>
       </c>
       <c r="I20" s="3">
         <v>900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K20" s="3">
+        <v>900</v>
+      </c>
+      <c r="L20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>800</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1120,32 +1193,38 @@
       <c r="E21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-11900</v>
+      <c r="F21" s="3">
+        <v>8400</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>12</v>
+      <c r="I21" s="3">
+        <v>-12000</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M21" s="3">
         <v>-10300</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1179,78 +1258,96 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>8300</v>
+      </c>
+      <c r="F23" s="3">
         <v>7800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-2200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-5600</v>
       </c>
-      <c r="G23" s="3">
-        <v>-12000</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-27600</v>
-      </c>
       <c r="I23" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-27700</v>
+      </c>
+      <c r="K23" s="3">
         <v>1100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>7600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-10800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-36700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F24" s="3">
         <v>500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>1400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>1100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>1200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1284,78 +1381,96 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>9300</v>
+      </c>
+      <c r="F26" s="3">
         <v>7300</v>
       </c>
-      <c r="E26" s="3">
-        <v>-3100</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-5700</v>
-      </c>
       <c r="G26" s="3">
-        <v>-13400</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>12</v>
+        <v>-3200</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-5800</v>
       </c>
       <c r="I26" s="3">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K26" s="3">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3">
         <v>6400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-10700</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>9300</v>
+      </c>
+      <c r="F27" s="3">
         <v>7300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-3500</v>
       </c>
-      <c r="F27" s="3">
-        <v>-7100</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-14700</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>12</v>
+      <c r="H27" s="3">
+        <v>-7200</v>
       </c>
       <c r="I27" s="3">
+        <v>-14800</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K27" s="3">
         <v>-800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>1800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-7900</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1389,8 +1504,14 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1424,8 +1545,14 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1459,8 +1586,14 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1494,78 +1627,96 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-1000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-600</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-900</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>12</v>
       </c>
       <c r="I32" s="3">
         <v>-900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="L32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-800</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>9300</v>
+      </c>
+      <c r="F33" s="3">
         <v>7300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-3500</v>
       </c>
-      <c r="F33" s="3">
-        <v>-7100</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-14700</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>12</v>
+      <c r="H33" s="3">
+        <v>-7200</v>
       </c>
       <c r="I33" s="3">
+        <v>-14800</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K33" s="3">
         <v>-800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>1800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-7900</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1599,83 +1750,101 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>9300</v>
+      </c>
+      <c r="F35" s="3">
         <v>7300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-3500</v>
       </c>
-      <c r="F35" s="3">
-        <v>-7100</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-14700</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>12</v>
+      <c r="H35" s="3">
+        <v>-7200</v>
       </c>
       <c r="I35" s="3">
+        <v>-14800</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K35" s="3">
         <v>-800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>1800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-7900</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1689,8 +1858,10 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1704,28 +1875,30 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>105500</v>
+        <v>120000</v>
       </c>
       <c r="E41" s="3">
-        <v>65500</v>
+        <v>96200</v>
       </c>
       <c r="F41" s="3">
-        <v>57800</v>
+        <v>106300</v>
       </c>
       <c r="G41" s="3">
-        <v>62200</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>12</v>
+        <v>65900</v>
+      </c>
+      <c r="H41" s="3">
+        <v>58200</v>
+      </c>
+      <c r="I41" s="3">
+        <v>62600</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>12</v>
@@ -1739,29 +1912,35 @@
       <c r="M41" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O41" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>23000</v>
+        <v>26100</v>
       </c>
       <c r="E42" s="3">
-        <v>52000</v>
+        <v>26100</v>
       </c>
       <c r="F42" s="3">
-        <v>14800</v>
+        <v>23100</v>
       </c>
       <c r="G42" s="3">
+        <v>52300</v>
+      </c>
+      <c r="H42" s="3">
+        <v>14900</v>
+      </c>
+      <c r="I42" s="3">
         <v>800</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="J42" s="3" t="s">
         <v>12</v>
       </c>
@@ -1774,29 +1953,35 @@
       <c r="M42" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>5700</v>
+        <v>2700</v>
       </c>
       <c r="E43" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F43" s="3">
+        <v>5800</v>
+      </c>
+      <c r="G43" s="3">
         <v>4900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>4500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>5400</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>12</v>
       </c>
@@ -1809,31 +1994,37 @@
       <c r="M43" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+        <v>3000</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -1844,28 +2035,34 @@
       <c r="M44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>18900</v>
+        <v>21800</v>
       </c>
       <c r="E45" s="3">
-        <v>17000</v>
+        <v>26000</v>
       </c>
       <c r="F45" s="3">
-        <v>20600</v>
+        <v>19000</v>
       </c>
       <c r="G45" s="3">
-        <v>15700</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>12</v>
+        <v>17100</v>
+      </c>
+      <c r="H45" s="3">
+        <v>20700</v>
+      </c>
+      <c r="I45" s="3">
+        <v>15800</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>12</v>
@@ -1879,28 +2076,34 @@
       <c r="M45" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>153100</v>
+        <v>172600</v>
       </c>
       <c r="E46" s="3">
-        <v>139300</v>
+        <v>155100</v>
       </c>
       <c r="F46" s="3">
-        <v>97700</v>
+        <v>154100</v>
       </c>
       <c r="G46" s="3">
-        <v>84100</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>12</v>
+        <v>140200</v>
+      </c>
+      <c r="H46" s="3">
+        <v>98300</v>
+      </c>
+      <c r="I46" s="3">
+        <v>84600</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>12</v>
@@ -1914,8 +2117,14 @@
       <c r="M46" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O46" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1949,29 +2158,35 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>12600</v>
+        <v>10500</v>
       </c>
       <c r="E48" s="3">
-        <v>14000</v>
+        <v>11600</v>
       </c>
       <c r="F48" s="3">
-        <v>15200</v>
+        <v>12700</v>
       </c>
       <c r="G48" s="3">
+        <v>14100</v>
+      </c>
+      <c r="H48" s="3">
+        <v>15300</v>
+      </c>
+      <c r="I48" s="3">
         <v>3500</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>12</v>
       </c>
@@ -1984,31 +2199,37 @@
       <c r="M48" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
-      </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
-        <v>0</v>
+        <v>1500</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="I49" s="3">
         <v>0</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
+      <c r="J49" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -2019,8 +2240,14 @@
       <c r="M49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2054,8 +2281,14 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2089,29 +2322,35 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>3200</v>
+        <v>3000</v>
       </c>
       <c r="E52" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F52" s="3">
+        <v>3300</v>
+      </c>
+      <c r="G52" s="3">
         <v>3000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>3500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>1400</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>12</v>
       </c>
@@ -2124,8 +2363,14 @@
       <c r="M52" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2159,28 +2404,34 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>168900</v>
+        <v>187600</v>
       </c>
       <c r="E54" s="3">
-        <v>156300</v>
+        <v>172500</v>
       </c>
       <c r="F54" s="3">
-        <v>116400</v>
+        <v>170100</v>
       </c>
       <c r="G54" s="3">
-        <v>88900</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>12</v>
+        <v>157300</v>
+      </c>
+      <c r="H54" s="3">
+        <v>117200</v>
+      </c>
+      <c r="I54" s="3">
+        <v>89500</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>12</v>
@@ -2194,8 +2445,14 @@
       <c r="M54" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2209,8 +2466,10 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2224,28 +2483,30 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>11100</v>
+      </c>
+      <c r="F57" s="3">
         <v>8600</v>
       </c>
-      <c r="E57" s="3">
-        <v>10400</v>
-      </c>
-      <c r="F57" s="3">
-        <v>9800</v>
-      </c>
       <c r="G57" s="3">
-        <v>9600</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>12</v>
+        <v>10500</v>
+      </c>
+      <c r="H57" s="3">
+        <v>9900</v>
+      </c>
+      <c r="I57" s="3">
+        <v>9700</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>12</v>
@@ -2259,8 +2520,14 @@
       <c r="M57" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2294,28 +2561,34 @@
       <c r="M58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>121900</v>
+        <v>122200</v>
       </c>
       <c r="E59" s="3">
-        <v>120600</v>
+        <v>117300</v>
       </c>
       <c r="F59" s="3">
-        <v>117300</v>
+        <v>122700</v>
       </c>
       <c r="G59" s="3">
-        <v>102100</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>12</v>
+        <v>121400</v>
+      </c>
+      <c r="H59" s="3">
+        <v>118100</v>
+      </c>
+      <c r="I59" s="3">
+        <v>102800</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>12</v>
@@ -2329,28 +2602,34 @@
       <c r="M59" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>130500</v>
+        <v>131600</v>
       </c>
       <c r="E60" s="3">
-        <v>131000</v>
+        <v>128500</v>
       </c>
       <c r="F60" s="3">
-        <v>127100</v>
+        <v>131300</v>
       </c>
       <c r="G60" s="3">
-        <v>111800</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>12</v>
+        <v>131900</v>
+      </c>
+      <c r="H60" s="3">
+        <v>128000</v>
+      </c>
+      <c r="I60" s="3">
+        <v>112500</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>12</v>
@@ -2364,8 +2643,14 @@
       <c r="M60" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O60" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2399,29 +2684,35 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E62" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F62" s="3">
         <v>7300</v>
       </c>
-      <c r="E62" s="3">
-        <v>9000</v>
-      </c>
-      <c r="F62" s="3">
-        <v>10400</v>
-      </c>
       <c r="G62" s="3">
+        <v>9100</v>
+      </c>
+      <c r="H62" s="3">
+        <v>10500</v>
+      </c>
+      <c r="I62" s="3">
         <v>1200</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>12</v>
       </c>
@@ -2434,8 +2725,14 @@
       <c r="M62" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2469,8 +2766,14 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2504,8 +2807,14 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2539,28 +2848,34 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>138000</v>
+        <v>137500</v>
       </c>
       <c r="E66" s="3">
-        <v>140000</v>
+        <v>135400</v>
       </c>
       <c r="F66" s="3">
-        <v>137600</v>
+        <v>139000</v>
       </c>
       <c r="G66" s="3">
-        <v>112900</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>12</v>
+        <v>141000</v>
+      </c>
+      <c r="H66" s="3">
+        <v>138500</v>
+      </c>
+      <c r="I66" s="3">
+        <v>113700</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>12</v>
@@ -2574,8 +2889,14 @@
       <c r="M66" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2589,8 +2910,10 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2624,8 +2947,14 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2659,8 +2988,14 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2671,16 +3006,16 @@
         <v>0</v>
       </c>
       <c r="F70" s="3">
-        <v>94400</v>
+        <v>0</v>
       </c>
       <c r="G70" s="3">
-        <v>93000</v>
+        <v>0</v>
       </c>
       <c r="H70" s="3">
-        <v>0</v>
+        <v>95000</v>
       </c>
       <c r="I70" s="3">
-        <v>0</v>
+        <v>93600</v>
       </c>
       <c r="J70" s="3">
         <v>0</v>
@@ -2694,8 +3029,14 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2729,28 +3070,34 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-133900</v>
+        <v>-110600</v>
       </c>
       <c r="E72" s="3">
-        <v>-141200</v>
+        <v>-125500</v>
       </c>
       <c r="F72" s="3">
-        <v>-138100</v>
+        <v>-134800</v>
       </c>
       <c r="G72" s="3">
-        <v>-132300</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>12</v>
+        <v>-142100</v>
+      </c>
+      <c r="H72" s="3">
+        <v>-139000</v>
+      </c>
+      <c r="I72" s="3">
+        <v>-133200</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>12</v>
@@ -2764,8 +3111,14 @@
       <c r="M72" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O72" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2799,8 +3152,14 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2834,8 +3193,14 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2869,28 +3234,34 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>30900</v>
+        <v>50100</v>
       </c>
       <c r="E76" s="3">
-        <v>16200</v>
+        <v>37100</v>
       </c>
       <c r="F76" s="3">
-        <v>-115500</v>
+        <v>31100</v>
       </c>
       <c r="G76" s="3">
-        <v>-117000</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>12</v>
+        <v>16400</v>
+      </c>
+      <c r="H76" s="3">
+        <v>-116300</v>
+      </c>
+      <c r="I76" s="3">
+        <v>-117800</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>12</v>
@@ -2904,8 +3275,14 @@
       <c r="M76" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O76" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2939,83 +3316,101 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>9300</v>
+      </c>
+      <c r="F81" s="3">
         <v>7300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-3500</v>
       </c>
-      <c r="F81" s="3">
-        <v>-7100</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-14700</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>12</v>
+      <c r="H81" s="3">
+        <v>-7200</v>
       </c>
       <c r="I81" s="3">
+        <v>-14800</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K81" s="3">
         <v>-800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>1800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-7900</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M81" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3029,8 +3424,10 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3040,11 +3437,11 @@
       <c r="E83" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G83" s="3">
-        <v>100</v>
+      <c r="F83" s="3">
+        <v>500</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>12</v>
@@ -3064,8 +3461,14 @@
       <c r="M83" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3099,8 +3502,14 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3134,8 +3543,14 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3169,8 +3584,14 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3204,8 +3625,14 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3239,8 +3666,14 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3250,11 +3683,11 @@
       <c r="E89" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G89" s="3">
-        <v>3900</v>
+      <c r="F89" s="3">
+        <v>32800</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>12</v>
@@ -3274,8 +3707,14 @@
       <c r="M89" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O89" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3289,13 +3728,15 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-5700</v>
+        <v>0</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -3321,11 +3762,17 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3359,8 +3806,14 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3394,8 +3847,14 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3405,11 +3864,11 @@
       <c r="E94" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G94" s="3">
-        <v>21200</v>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>12</v>
@@ -3429,8 +3888,14 @@
       <c r="M94" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3444,8 +3909,10 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3479,8 +3946,14 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3514,8 +3987,14 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3549,8 +4028,14 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3584,43 +4069,55 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+        <v>34400</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3630,11 +4127,11 @@
       <c r="E101" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G101" s="3">
-        <v>300</v>
+      <c r="F101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>12</v>
@@ -3654,8 +4151,14 @@
       <c r="M101" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -3665,11 +4168,11 @@
       <c r="E102" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F102" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G102" s="3">
-        <v>25400</v>
+      <c r="F102" s="3">
+        <v>69200</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>12</v>
@@ -3687,6 +4190,12 @@
         <v>12</v>
       </c>
       <c r="M102" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N102" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O102" s="3" t="s">
         <v>12</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/QSG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QSG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
   <si>
     <t>QSG</t>
   </si>
@@ -656,117 +656,124 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>136300</v>
+        <v>130600</v>
       </c>
       <c r="E8" s="3">
-        <v>120800</v>
+        <v>135500</v>
       </c>
       <c r="F8" s="3">
-        <v>115200</v>
+        <v>120100</v>
       </c>
       <c r="G8" s="3">
-        <v>112200</v>
+        <v>114400</v>
       </c>
       <c r="H8" s="3">
-        <v>109300</v>
+        <v>111500</v>
       </c>
       <c r="I8" s="3">
-        <v>91700</v>
+        <v>108600</v>
       </c>
       <c r="J8" s="3">
+        <v>91100</v>
+      </c>
+      <c r="K8" s="3">
         <v>87400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>95400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>111000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>102500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>86000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>81200</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -774,81 +781,87 @@
         <v>20200</v>
       </c>
       <c r="E9" s="3">
-        <v>16400</v>
+        <v>20000</v>
       </c>
       <c r="F9" s="3">
-        <v>16100</v>
+        <v>16300</v>
       </c>
       <c r="G9" s="3">
+        <v>16000</v>
+      </c>
+      <c r="H9" s="3">
         <v>14000</v>
       </c>
-      <c r="H9" s="3">
-        <v>13800</v>
-      </c>
       <c r="I9" s="3">
+        <v>13700</v>
+      </c>
+      <c r="J9" s="3">
         <v>10400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>15000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>31600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>27900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>11900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>10500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>7600</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>116100</v>
+        <v>110500</v>
       </c>
       <c r="E10" s="3">
-        <v>104400</v>
+        <v>115400</v>
       </c>
       <c r="F10" s="3">
-        <v>99000</v>
+        <v>103700</v>
       </c>
       <c r="G10" s="3">
-        <v>98200</v>
+        <v>98400</v>
       </c>
       <c r="H10" s="3">
-        <v>95500</v>
+        <v>97600</v>
       </c>
       <c r="I10" s="3">
-        <v>81200</v>
+        <v>94900</v>
       </c>
       <c r="J10" s="3">
+        <v>80700</v>
+      </c>
+      <c r="K10" s="3">
         <v>72500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>63800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>83200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>90600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>75600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>73600</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -864,49 +877,53 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E12" s="3">
         <v>5700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>6100</v>
       </c>
-      <c r="F12" s="3">
-        <v>7500</v>
-      </c>
       <c r="G12" s="3">
+        <v>7400</v>
+      </c>
+      <c r="H12" s="3">
         <v>6900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>8900</v>
       </c>
-      <c r="I12" s="3">
-        <v>7300</v>
-      </c>
       <c r="J12" s="3">
+        <v>7200</v>
+      </c>
+      <c r="K12" s="3">
         <v>18400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>13100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>14200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>5800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>10700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -946,8 +963,11 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -987,8 +1007,11 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1028,8 +1051,11 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1042,90 +1068,97 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>122100</v>
+        <v>131300</v>
       </c>
       <c r="E17" s="3">
+        <v>121300</v>
+      </c>
+      <c r="F17" s="3">
+        <v>114000</v>
+      </c>
+      <c r="G17" s="3">
+        <v>107900</v>
+      </c>
+      <c r="H17" s="3">
         <v>114700</v>
       </c>
-      <c r="F17" s="3">
-        <v>108500</v>
-      </c>
-      <c r="G17" s="3">
-        <v>115400</v>
-      </c>
-      <c r="H17" s="3">
-        <v>115500</v>
-      </c>
       <c r="I17" s="3">
-        <v>104700</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K17" s="3">
+        <v>114800</v>
+      </c>
+      <c r="J17" s="3">
+        <v>104000</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L17" s="3">
         <v>95200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>103700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>114200</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>14200</v>
+        <v>-700</v>
       </c>
       <c r="E18" s="3">
+        <v>14100</v>
+      </c>
+      <c r="F18" s="3">
         <v>6100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>6600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-3200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-6200</v>
       </c>
-      <c r="I18" s="3">
-        <v>-13000</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="J18" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L18" s="3">
         <v>200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>7300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-11700</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1141,49 +1174,53 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E20" s="3">
         <v>600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>900</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L20" s="3">
         <v>900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>800</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1193,20 +1230,20 @@
       <c r="E21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F21" s="3">
-        <v>8400</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>12</v>
+      <c r="F21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="3">
+        <v>8300</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I21" s="3">
-        <v>-12000</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>12</v>
+      <c r="I21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-11900</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>12</v>
@@ -1214,17 +1251,20 @@
       <c r="L21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N21" s="3">
         <v>-10300</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1264,90 +1304,99 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>14900</v>
+        <v>700</v>
       </c>
       <c r="E23" s="3">
+        <v>14800</v>
+      </c>
+      <c r="F23" s="3">
         <v>8300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>7800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-5600</v>
       </c>
-      <c r="I23" s="3">
-        <v>-12100</v>
-      </c>
       <c r="J23" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="K23" s="3">
         <v>-27700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-10800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-36700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E24" s="3">
         <v>-100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-100</v>
-      </c>
-      <c r="N24" s="3">
-        <v>100</v>
       </c>
       <c r="O24" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1387,90 +1436,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>15000</v>
+        <v>2000</v>
       </c>
       <c r="E26" s="3">
-        <v>9300</v>
+        <v>14900</v>
       </c>
       <c r="F26" s="3">
+        <v>9200</v>
+      </c>
+      <c r="G26" s="3">
         <v>7300</v>
       </c>
-      <c r="G26" s="3">
-        <v>-3200</v>
-      </c>
       <c r="H26" s="3">
-        <v>-5800</v>
+        <v>-3100</v>
       </c>
       <c r="I26" s="3">
-        <v>-13500</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K26" s="3">
-        <v>0</v>
+        <v>-5700</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-13400</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="L26" s="3">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3">
         <v>6400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-10700</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>15000</v>
+        <v>2000</v>
       </c>
       <c r="E27" s="3">
-        <v>9300</v>
+        <v>14900</v>
       </c>
       <c r="F27" s="3">
+        <v>9200</v>
+      </c>
+      <c r="G27" s="3">
         <v>7300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3500</v>
       </c>
-      <c r="H27" s="3">
-        <v>-7200</v>
-      </c>
       <c r="I27" s="3">
-        <v>-14800</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K27" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-14700</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L27" s="3">
         <v>-800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7900</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1510,8 +1568,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1551,8 +1612,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1592,8 +1656,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1633,90 +1700,99 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-900</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L32" s="3">
         <v>-900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-800</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>15000</v>
+        <v>2000</v>
       </c>
       <c r="E33" s="3">
-        <v>9300</v>
+        <v>14900</v>
       </c>
       <c r="F33" s="3">
+        <v>9200</v>
+      </c>
+      <c r="G33" s="3">
         <v>7300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3500</v>
       </c>
-      <c r="H33" s="3">
-        <v>-7200</v>
-      </c>
       <c r="I33" s="3">
-        <v>-14800</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K33" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-14700</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L33" s="3">
         <v>-800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7900</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1756,95 +1832,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>15000</v>
+        <v>2000</v>
       </c>
       <c r="E35" s="3">
-        <v>9300</v>
+        <v>14900</v>
       </c>
       <c r="F35" s="3">
+        <v>9200</v>
+      </c>
+      <c r="G35" s="3">
         <v>7300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3500</v>
       </c>
-      <c r="H35" s="3">
-        <v>-7200</v>
-      </c>
       <c r="I35" s="3">
-        <v>-14800</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K35" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-14700</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L35" s="3">
         <v>-800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7900</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1860,8 +1945,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1877,31 +1963,32 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>120000</v>
+        <v>134200</v>
       </c>
       <c r="E41" s="3">
-        <v>96200</v>
+        <v>119200</v>
       </c>
       <c r="F41" s="3">
-        <v>106300</v>
+        <v>95600</v>
       </c>
       <c r="G41" s="3">
-        <v>65900</v>
+        <v>105600</v>
       </c>
       <c r="H41" s="3">
-        <v>58200</v>
+        <v>65500</v>
       </c>
       <c r="I41" s="3">
-        <v>62600</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>12</v>
+        <v>57900</v>
+      </c>
+      <c r="J41" s="3">
+        <v>62200</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>12</v>
@@ -1918,32 +2005,35 @@
       <c r="O41" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>26100</v>
+        <v>24600</v>
       </c>
       <c r="E42" s="3">
-        <v>26100</v>
+        <v>26000</v>
       </c>
       <c r="F42" s="3">
-        <v>23100</v>
+        <v>26000</v>
       </c>
       <c r="G42" s="3">
-        <v>52300</v>
+        <v>23000</v>
       </c>
       <c r="H42" s="3">
-        <v>14900</v>
+        <v>52000</v>
       </c>
       <c r="I42" s="3">
+        <v>14800</v>
+      </c>
+      <c r="J42" s="3">
         <v>800</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="K42" s="3" t="s">
         <v>12</v>
       </c>
@@ -1959,32 +2049,35 @@
       <c r="O42" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E43" s="3">
         <v>2700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3800</v>
       </c>
-      <c r="F43" s="3">
-        <v>5800</v>
-      </c>
       <c r="G43" s="3">
+        <v>5700</v>
+      </c>
+      <c r="H43" s="3">
         <v>4900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5400</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>12</v>
       </c>
@@ -2000,20 +2093,23 @@
       <c r="O43" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E44" s="3">
         <v>2000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3000</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="G44" s="3" t="s">
         <v>12</v>
       </c>
@@ -2026,8 +2122,8 @@
       <c r="J44" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2041,31 +2137,34 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>21800</v>
+        <v>25300</v>
       </c>
       <c r="E45" s="3">
-        <v>26000</v>
+        <v>21700</v>
       </c>
       <c r="F45" s="3">
-        <v>19000</v>
+        <v>25800</v>
       </c>
       <c r="G45" s="3">
-        <v>17100</v>
+        <v>18900</v>
       </c>
       <c r="H45" s="3">
-        <v>20700</v>
+        <v>17000</v>
       </c>
       <c r="I45" s="3">
-        <v>15800</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>12</v>
+        <v>20600</v>
+      </c>
+      <c r="J45" s="3">
+        <v>15700</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>12</v>
@@ -2082,31 +2181,34 @@
       <c r="O45" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>172600</v>
+        <v>189400</v>
       </c>
       <c r="E46" s="3">
-        <v>155100</v>
+        <v>171600</v>
       </c>
       <c r="F46" s="3">
         <v>154100</v>
       </c>
       <c r="G46" s="3">
-        <v>140200</v>
+        <v>153200</v>
       </c>
       <c r="H46" s="3">
-        <v>98300</v>
+        <v>139300</v>
       </c>
       <c r="I46" s="3">
-        <v>84600</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>12</v>
+        <v>97700</v>
+      </c>
+      <c r="J46" s="3">
+        <v>84100</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>12</v>
@@ -2123,8 +2225,11 @@
       <c r="O46" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2164,32 +2269,35 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>10500</v>
+        <v>9900</v>
       </c>
       <c r="E48" s="3">
-        <v>11600</v>
+        <v>10400</v>
       </c>
       <c r="F48" s="3">
-        <v>12700</v>
+        <v>11500</v>
       </c>
       <c r="G48" s="3">
-        <v>14100</v>
+        <v>12600</v>
       </c>
       <c r="H48" s="3">
-        <v>15300</v>
+        <v>14000</v>
       </c>
       <c r="I48" s="3">
+        <v>15200</v>
+      </c>
+      <c r="J48" s="3">
         <v>3500</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>12</v>
       </c>
@@ -2205,8 +2313,11 @@
       <c r="O48" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2214,25 +2325,25 @@
         <v>1400</v>
       </c>
       <c r="E49" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F49" s="3">
         <v>1500</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="G49" s="3" t="s">
         <v>12</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K49" s="3">
-        <v>0</v>
+      <c r="I49" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
@@ -2246,8 +2357,11 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2287,8 +2401,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2328,32 +2445,35 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E52" s="3">
         <v>3000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4300</v>
       </c>
-      <c r="F52" s="3">
-        <v>3300</v>
-      </c>
       <c r="G52" s="3">
+        <v>3200</v>
+      </c>
+      <c r="H52" s="3">
         <v>3000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1400</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>12</v>
       </c>
@@ -2369,8 +2489,11 @@
       <c r="O52" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2410,31 +2533,34 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>187600</v>
+        <v>205500</v>
       </c>
       <c r="E54" s="3">
-        <v>172500</v>
+        <v>186400</v>
       </c>
       <c r="F54" s="3">
-        <v>170100</v>
+        <v>171400</v>
       </c>
       <c r="G54" s="3">
-        <v>157300</v>
+        <v>169000</v>
       </c>
       <c r="H54" s="3">
-        <v>117200</v>
+        <v>156300</v>
       </c>
       <c r="I54" s="3">
-        <v>89500</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>12</v>
+        <v>116500</v>
+      </c>
+      <c r="J54" s="3">
+        <v>89000</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>12</v>
@@ -2451,8 +2577,11 @@
       <c r="O54" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2468,8 +2597,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2485,31 +2615,32 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>9400</v>
+        <v>12000</v>
       </c>
       <c r="E57" s="3">
+        <v>9300</v>
+      </c>
+      <c r="F57" s="3">
         <v>11100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8600</v>
       </c>
-      <c r="G57" s="3">
-        <v>10500</v>
-      </c>
       <c r="H57" s="3">
-        <v>9900</v>
+        <v>10400</v>
       </c>
       <c r="I57" s="3">
-        <v>9700</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>12</v>
+        <v>9800</v>
+      </c>
+      <c r="J57" s="3">
+        <v>9600</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>12</v>
@@ -2526,8 +2657,11 @@
       <c r="O57" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2567,31 +2701,34 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>122200</v>
+        <v>138600</v>
       </c>
       <c r="E59" s="3">
-        <v>117300</v>
+        <v>121500</v>
       </c>
       <c r="F59" s="3">
-        <v>122700</v>
+        <v>116600</v>
       </c>
       <c r="G59" s="3">
-        <v>121400</v>
+        <v>121900</v>
       </c>
       <c r="H59" s="3">
-        <v>118100</v>
+        <v>120700</v>
       </c>
       <c r="I59" s="3">
-        <v>102800</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>12</v>
+        <v>117400</v>
+      </c>
+      <c r="J59" s="3">
+        <v>102200</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>12</v>
@@ -2608,31 +2745,34 @@
       <c r="O59" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>131600</v>
+        <v>150600</v>
       </c>
       <c r="E60" s="3">
-        <v>128500</v>
+        <v>130800</v>
       </c>
       <c r="F60" s="3">
-        <v>131300</v>
+        <v>127700</v>
       </c>
       <c r="G60" s="3">
-        <v>131900</v>
+        <v>130500</v>
       </c>
       <c r="H60" s="3">
-        <v>128000</v>
+        <v>131100</v>
       </c>
       <c r="I60" s="3">
-        <v>112500</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>12</v>
+        <v>127200</v>
+      </c>
+      <c r="J60" s="3">
+        <v>111800</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>12</v>
@@ -2649,8 +2789,11 @@
       <c r="O60" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2690,32 +2833,35 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E62" s="3">
         <v>5800</v>
       </c>
-      <c r="E62" s="3">
-        <v>7000</v>
-      </c>
       <c r="F62" s="3">
+        <v>6900</v>
+      </c>
+      <c r="G62" s="3">
         <v>7300</v>
       </c>
-      <c r="G62" s="3">
-        <v>9100</v>
-      </c>
       <c r="H62" s="3">
-        <v>10500</v>
+        <v>9000</v>
       </c>
       <c r="I62" s="3">
+        <v>10400</v>
+      </c>
+      <c r="J62" s="3">
         <v>1200</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>12</v>
       </c>
@@ -2731,8 +2877,11 @@
       <c r="O62" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2772,8 +2921,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2813,8 +2965,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2854,31 +3009,34 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>137500</v>
+        <v>154700</v>
       </c>
       <c r="E66" s="3">
-        <v>135400</v>
+        <v>136600</v>
       </c>
       <c r="F66" s="3">
-        <v>139000</v>
+        <v>134600</v>
       </c>
       <c r="G66" s="3">
-        <v>141000</v>
+        <v>138100</v>
       </c>
       <c r="H66" s="3">
-        <v>138500</v>
+        <v>140100</v>
       </c>
       <c r="I66" s="3">
-        <v>113700</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>12</v>
+        <v>137600</v>
+      </c>
+      <c r="J66" s="3">
+        <v>113000</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>12</v>
@@ -2895,8 +3053,11 @@
       <c r="O66" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2912,8 +3073,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2953,8 +3115,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2994,8 +3159,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3012,13 +3180,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="3">
-        <v>95000</v>
+        <v>0</v>
       </c>
       <c r="I70" s="3">
-        <v>93600</v>
+        <v>94500</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>93100</v>
       </c>
       <c r="K70" s="3">
         <v>0</v>
@@ -3035,8 +3203,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3076,31 +3247,34 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-110600</v>
+        <v>-107900</v>
       </c>
       <c r="E72" s="3">
-        <v>-125500</v>
+        <v>-109900</v>
       </c>
       <c r="F72" s="3">
-        <v>-134800</v>
+        <v>-124800</v>
       </c>
       <c r="G72" s="3">
-        <v>-142100</v>
+        <v>-134000</v>
       </c>
       <c r="H72" s="3">
-        <v>-139000</v>
+        <v>-141300</v>
       </c>
       <c r="I72" s="3">
-        <v>-133200</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>12</v>
+        <v>-138100</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-132400</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>12</v>
@@ -3117,8 +3291,11 @@
       <c r="O72" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3158,8 +3335,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3199,8 +3379,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3240,31 +3423,34 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>50100</v>
+        <v>50900</v>
       </c>
       <c r="E76" s="3">
-        <v>37100</v>
+        <v>49800</v>
       </c>
       <c r="F76" s="3">
-        <v>31100</v>
+        <v>36800</v>
       </c>
       <c r="G76" s="3">
-        <v>16400</v>
+        <v>30900</v>
       </c>
       <c r="H76" s="3">
-        <v>-116300</v>
+        <v>16200</v>
       </c>
       <c r="I76" s="3">
-        <v>-117800</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>12</v>
+        <v>-115600</v>
+      </c>
+      <c r="J76" s="3">
+        <v>-117100</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>12</v>
@@ -3281,8 +3467,11 @@
       <c r="O76" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3322,95 +3511,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>15000</v>
+        <v>2000</v>
       </c>
       <c r="E81" s="3">
-        <v>9300</v>
+        <v>14900</v>
       </c>
       <c r="F81" s="3">
+        <v>9200</v>
+      </c>
+      <c r="G81" s="3">
         <v>7300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3500</v>
       </c>
-      <c r="H81" s="3">
-        <v>-7200</v>
-      </c>
       <c r="I81" s="3">
-        <v>-14800</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K81" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-14700</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L81" s="3">
         <v>-800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7900</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3426,8 +3624,9 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3437,12 +3636,12 @@
       <c r="E83" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F83" s="3">
+      <c r="F83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G83" s="3">
         <v>500</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="H83" s="3" t="s">
         <v>12</v>
       </c>
@@ -3467,8 +3666,11 @@
       <c r="O83" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3508,8 +3710,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3549,8 +3754,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3590,8 +3798,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3631,8 +3842,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3672,8 +3886,11 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3683,11 +3900,11 @@
       <c r="E89" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F89" s="3">
-        <v>32800</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>12</v>
+      <c r="F89" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G89" s="3">
+        <v>32600</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>12</v>
@@ -3713,8 +3930,11 @@
       <c r="O89" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3730,8 +3950,9 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3768,11 +3989,14 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3812,8 +4036,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3853,8 +4080,11 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3864,11 +4094,11 @@
       <c r="E94" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>12</v>
+      <c r="F94" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>12</v>
@@ -3894,8 +4124,11 @@
       <c r="O94" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3911,8 +4144,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3952,8 +4186,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3993,8 +4230,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4034,8 +4274,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4075,8 +4318,11 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4086,11 +4332,11 @@
       <c r="E100" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F100" s="3">
-        <v>34400</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>12</v>
+      <c r="F100" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G100" s="3">
+        <v>34200</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>12</v>
@@ -4101,8 +4347,8 @@
       <c r="J100" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -4110,14 +4356,17 @@
       <c r="M100" s="3">
         <v>0</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>12</v>
+      <c r="N100" s="3">
+        <v>0</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4127,12 +4376,12 @@
       <c r="E101" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F101" s="3">
+      <c r="F101" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G101" s="3">
         <v>2000</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="H101" s="3" t="s">
         <v>12</v>
       </c>
@@ -4157,8 +4406,11 @@
       <c r="O101" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4168,11 +4420,11 @@
       <c r="E102" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F102" s="3">
-        <v>69200</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>12</v>
+      <c r="F102" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G102" s="3">
+        <v>68800</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>12</v>
@@ -4196,6 +4448,9 @@
         <v>12</v>
       </c>
       <c r="O102" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P102" s="3" t="s">
         <v>12</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/QSG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QSG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="92">
   <si>
     <t>QSG</t>
   </si>
@@ -656,212 +656,225 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>130600</v>
+        <v>141000</v>
       </c>
       <c r="E8" s="3">
-        <v>135500</v>
+        <v>133300</v>
       </c>
       <c r="F8" s="3">
-        <v>120100</v>
+        <v>138200</v>
       </c>
       <c r="G8" s="3">
-        <v>114400</v>
+        <v>122500</v>
       </c>
       <c r="H8" s="3">
-        <v>111500</v>
+        <v>116800</v>
       </c>
       <c r="I8" s="3">
-        <v>108600</v>
+        <v>113800</v>
       </c>
       <c r="J8" s="3">
+        <v>110900</v>
+      </c>
+      <c r="K8" s="3">
         <v>91100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>87400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>95400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>111000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>102500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>86000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>81200</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>20200</v>
+        <v>19900</v>
       </c>
       <c r="E9" s="3">
-        <v>20000</v>
+        <v>20600</v>
       </c>
       <c r="F9" s="3">
-        <v>16300</v>
+        <v>20400</v>
       </c>
       <c r="G9" s="3">
-        <v>16000</v>
+        <v>16700</v>
       </c>
       <c r="H9" s="3">
+        <v>16400</v>
+      </c>
+      <c r="I9" s="3">
+        <v>14200</v>
+      </c>
+      <c r="J9" s="3">
         <v>14000</v>
       </c>
-      <c r="I9" s="3">
-        <v>13700</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>10400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>15000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>31600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>27900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>11900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>7600</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>110500</v>
+        <v>121100</v>
       </c>
       <c r="E10" s="3">
-        <v>115400</v>
+        <v>112700</v>
       </c>
       <c r="F10" s="3">
-        <v>103700</v>
+        <v>117800</v>
       </c>
       <c r="G10" s="3">
-        <v>98400</v>
+        <v>105900</v>
       </c>
       <c r="H10" s="3">
-        <v>97600</v>
+        <v>100400</v>
       </c>
       <c r="I10" s="3">
-        <v>94900</v>
+        <v>99600</v>
       </c>
       <c r="J10" s="3">
+        <v>96900</v>
+      </c>
+      <c r="K10" s="3">
         <v>80700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>72500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>63800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>83200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>90600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>75600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>73600</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -878,52 +891,56 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>5400</v>
+        <v>3000</v>
       </c>
       <c r="E12" s="3">
-        <v>5700</v>
+        <v>5500</v>
       </c>
       <c r="F12" s="3">
-        <v>6100</v>
+        <v>5800</v>
       </c>
       <c r="G12" s="3">
-        <v>7400</v>
+        <v>6200</v>
       </c>
       <c r="H12" s="3">
-        <v>6900</v>
+        <v>7600</v>
       </c>
       <c r="I12" s="3">
-        <v>8900</v>
+        <v>7000</v>
       </c>
       <c r="J12" s="3">
+        <v>9100</v>
+      </c>
+      <c r="K12" s="3">
         <v>7200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>18400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>13100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>14200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>10700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -966,31 +983,34 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>1400</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1010,8 +1030,11 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1054,8 +1077,11 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,96 +1095,103 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>131300</v>
+        <v>107700</v>
       </c>
       <c r="E17" s="3">
-        <v>121300</v>
+        <v>134000</v>
       </c>
       <c r="F17" s="3">
-        <v>114000</v>
+        <v>123800</v>
       </c>
       <c r="G17" s="3">
-        <v>107900</v>
+        <v>116300</v>
       </c>
       <c r="H17" s="3">
-        <v>114700</v>
+        <v>110100</v>
       </c>
       <c r="I17" s="3">
-        <v>114800</v>
+        <v>117100</v>
       </c>
       <c r="J17" s="3">
+        <v>117100</v>
+      </c>
+      <c r="K17" s="3">
         <v>104000</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M17" s="3">
         <v>95200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>103700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>114200</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>33300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-700</v>
       </c>
-      <c r="E18" s="3">
-        <v>14100</v>
-      </c>
       <c r="F18" s="3">
-        <v>6100</v>
+        <v>14400</v>
       </c>
       <c r="G18" s="3">
-        <v>6600</v>
+        <v>6200</v>
       </c>
       <c r="H18" s="3">
-        <v>-3200</v>
+        <v>6700</v>
       </c>
       <c r="I18" s="3">
-        <v>-6200</v>
+        <v>-3300</v>
       </c>
       <c r="J18" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="K18" s="3">
         <v>-12900</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M18" s="3">
         <v>200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>7300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-11700</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,52 +1208,56 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E20" s="3">
         <v>1400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
+        <v>700</v>
+      </c>
+      <c r="G20" s="3">
+        <v>2200</v>
+      </c>
+      <c r="H20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J20" s="3">
         <v>600</v>
       </c>
-      <c r="F20" s="3">
-        <v>2200</v>
-      </c>
-      <c r="G20" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H20" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I20" s="3">
-        <v>600</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>900</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M20" s="3">
         <v>900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>800</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1233,38 +1270,41 @@
       <c r="F21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G21" s="3">
-        <v>8300</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>12</v>
+      <c r="G21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H21" s="3">
+        <v>8500</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J21" s="3">
+      <c r="J21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K21" s="3">
         <v>-11900</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>12</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O21" s="3">
         <v>-10300</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1307,96 +1347,105 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>34500</v>
+      </c>
+      <c r="E23" s="3">
         <v>700</v>
       </c>
-      <c r="E23" s="3">
-        <v>14800</v>
-      </c>
       <c r="F23" s="3">
-        <v>8300</v>
+        <v>15100</v>
       </c>
       <c r="G23" s="3">
-        <v>7800</v>
+        <v>8400</v>
       </c>
       <c r="H23" s="3">
-        <v>-2200</v>
+        <v>7900</v>
       </c>
       <c r="I23" s="3">
-        <v>-5600</v>
+        <v>-2300</v>
       </c>
       <c r="J23" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="K23" s="3">
         <v>-12000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-27700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>7600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-10800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-36700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
-        <v>-900</v>
-      </c>
       <c r="G24" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="H24" s="3">
         <v>500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-100</v>
-      </c>
-      <c r="O24" s="3">
-        <v>100</v>
       </c>
       <c r="P24" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,96 +1488,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>2000</v>
+        <v>27700</v>
       </c>
       <c r="E26" s="3">
-        <v>14900</v>
+        <v>2100</v>
       </c>
       <c r="F26" s="3">
-        <v>9200</v>
+        <v>15200</v>
       </c>
       <c r="G26" s="3">
-        <v>7300</v>
+        <v>9400</v>
       </c>
       <c r="H26" s="3">
-        <v>-3100</v>
+        <v>7400</v>
       </c>
       <c r="I26" s="3">
-        <v>-5700</v>
+        <v>-3200</v>
       </c>
       <c r="J26" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="K26" s="3">
         <v>-13400</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L26" s="3">
-        <v>0</v>
+      <c r="L26" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="M26" s="3">
+        <v>0</v>
+      </c>
+      <c r="N26" s="3">
         <v>6400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-10700</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>2000</v>
+        <v>27700</v>
       </c>
       <c r="E27" s="3">
-        <v>14900</v>
+        <v>2100</v>
       </c>
       <c r="F27" s="3">
-        <v>9200</v>
+        <v>15200</v>
       </c>
       <c r="G27" s="3">
-        <v>7300</v>
+        <v>9400</v>
       </c>
       <c r="H27" s="3">
-        <v>-3500</v>
+        <v>7400</v>
       </c>
       <c r="I27" s="3">
-        <v>-7100</v>
+        <v>-3600</v>
       </c>
       <c r="J27" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="K27" s="3">
         <v>-14700</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M27" s="3">
         <v>-800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-7900</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,8 +1629,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1615,8 +1676,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1723,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,96 +1770,105 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J32" s="3">
         <v>-600</v>
       </c>
-      <c r="F32" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-600</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-900</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M32" s="3">
         <v>-900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-800</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>2000</v>
+        <v>27700</v>
       </c>
       <c r="E33" s="3">
-        <v>14900</v>
+        <v>2100</v>
       </c>
       <c r="F33" s="3">
-        <v>9200</v>
+        <v>15200</v>
       </c>
       <c r="G33" s="3">
-        <v>7300</v>
+        <v>9400</v>
       </c>
       <c r="H33" s="3">
-        <v>-3500</v>
+        <v>7400</v>
       </c>
       <c r="I33" s="3">
-        <v>-7100</v>
+        <v>-3600</v>
       </c>
       <c r="J33" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="K33" s="3">
         <v>-14700</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M33" s="3">
         <v>-800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-7900</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,101 +1911,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>2000</v>
+        <v>27700</v>
       </c>
       <c r="E35" s="3">
-        <v>14900</v>
+        <v>2100</v>
       </c>
       <c r="F35" s="3">
-        <v>9200</v>
+        <v>15200</v>
       </c>
       <c r="G35" s="3">
-        <v>7300</v>
+        <v>9400</v>
       </c>
       <c r="H35" s="3">
-        <v>-3500</v>
+        <v>7400</v>
       </c>
       <c r="I35" s="3">
-        <v>-7100</v>
+        <v>-3600</v>
       </c>
       <c r="J35" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="K35" s="3">
         <v>-14700</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M35" s="3">
         <v>-800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-7900</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2031,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,35 +2050,36 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>134200</v>
+        <v>110000</v>
       </c>
       <c r="E41" s="3">
-        <v>119200</v>
+        <v>137000</v>
       </c>
       <c r="F41" s="3">
-        <v>95600</v>
+        <v>121700</v>
       </c>
       <c r="G41" s="3">
-        <v>105600</v>
+        <v>97500</v>
       </c>
       <c r="H41" s="3">
-        <v>65500</v>
+        <v>107700</v>
       </c>
       <c r="I41" s="3">
-        <v>57900</v>
+        <v>66800</v>
       </c>
       <c r="J41" s="3">
+        <v>59000</v>
+      </c>
+      <c r="K41" s="3">
         <v>62200</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>12</v>
       </c>
@@ -2008,35 +2095,38 @@
       <c r="P41" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>24600</v>
+        <v>34700</v>
       </c>
       <c r="E42" s="3">
-        <v>26000</v>
+        <v>25100</v>
       </c>
       <c r="F42" s="3">
-        <v>26000</v>
+        <v>26500</v>
       </c>
       <c r="G42" s="3">
-        <v>23000</v>
+        <v>26500</v>
       </c>
       <c r="H42" s="3">
-        <v>52000</v>
+        <v>23400</v>
       </c>
       <c r="I42" s="3">
-        <v>14800</v>
+        <v>53100</v>
       </c>
       <c r="J42" s="3">
+        <v>15100</v>
+      </c>
+      <c r="K42" s="3">
         <v>800</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="L42" s="3" t="s">
         <v>12</v>
       </c>
@@ -2052,35 +2142,38 @@
       <c r="P42" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E43" s="3">
         <v>4300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3800</v>
       </c>
-      <c r="G43" s="3">
-        <v>5700</v>
-      </c>
       <c r="H43" s="3">
-        <v>4900</v>
+        <v>5800</v>
       </c>
       <c r="I43" s="3">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="J43" s="3">
+        <v>4600</v>
+      </c>
+      <c r="K43" s="3">
         <v>5400</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>12</v>
       </c>
@@ -2096,22 +2189,25 @@
       <c r="P43" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>900</v>
+      </c>
+      <c r="E44" s="3">
         <v>1000</v>
       </c>
-      <c r="E44" s="3">
-        <v>2000</v>
-      </c>
       <c r="F44" s="3">
-        <v>3000</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>12</v>
+        <v>2100</v>
+      </c>
+      <c r="G44" s="3">
+        <v>3100</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>12</v>
@@ -2125,8 +2221,8 @@
       <c r="K44" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2140,35 +2236,38 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>25300</v>
+        <v>15700</v>
       </c>
       <c r="E45" s="3">
-        <v>21700</v>
+        <v>25800</v>
       </c>
       <c r="F45" s="3">
-        <v>25800</v>
+        <v>22100</v>
       </c>
       <c r="G45" s="3">
-        <v>18900</v>
+        <v>26300</v>
       </c>
       <c r="H45" s="3">
-        <v>17000</v>
+        <v>19300</v>
       </c>
       <c r="I45" s="3">
-        <v>20600</v>
+        <v>17300</v>
       </c>
       <c r="J45" s="3">
+        <v>21000</v>
+      </c>
+      <c r="K45" s="3">
         <v>15700</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>12</v>
       </c>
@@ -2184,35 +2283,38 @@
       <c r="P45" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>189400</v>
+        <v>187400</v>
       </c>
       <c r="E46" s="3">
-        <v>171600</v>
+        <v>193300</v>
       </c>
       <c r="F46" s="3">
-        <v>154100</v>
+        <v>175100</v>
       </c>
       <c r="G46" s="3">
-        <v>153200</v>
+        <v>157300</v>
       </c>
       <c r="H46" s="3">
-        <v>139300</v>
+        <v>156300</v>
       </c>
       <c r="I46" s="3">
-        <v>97700</v>
+        <v>142200</v>
       </c>
       <c r="J46" s="3">
+        <v>99700</v>
+      </c>
+      <c r="K46" s="3">
         <v>84100</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>12</v>
       </c>
@@ -2228,31 +2330,34 @@
       <c r="P46" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>1300</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2272,35 +2377,38 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>9900</v>
+        <v>9200</v>
       </c>
       <c r="E48" s="3">
-        <v>10400</v>
+        <v>10100</v>
       </c>
       <c r="F48" s="3">
-        <v>11500</v>
+        <v>10600</v>
       </c>
       <c r="G48" s="3">
-        <v>12600</v>
+        <v>11800</v>
       </c>
       <c r="H48" s="3">
-        <v>14000</v>
+        <v>12900</v>
       </c>
       <c r="I48" s="3">
-        <v>15200</v>
+        <v>14300</v>
       </c>
       <c r="J48" s="3">
+        <v>15600</v>
+      </c>
+      <c r="K48" s="3">
         <v>3500</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>12</v>
       </c>
@@ -2316,13 +2424,16 @@
       <c r="P48" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
-        <v>1400</v>
+      <c r="D49" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="E49" s="3">
         <v>1400</v>
@@ -2330,8 +2441,8 @@
       <c r="F49" s="3">
         <v>1500</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>12</v>
+      <c r="G49" s="3">
+        <v>1500</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>12</v>
@@ -2339,14 +2450,14 @@
       <c r="I49" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L49" s="3">
-        <v>0</v>
+      <c r="J49" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -2360,8 +2471,11 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2518,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,35 +2565,38 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4800</v>
+        <v>3100</v>
       </c>
       <c r="E52" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F52" s="3">
         <v>3000</v>
       </c>
-      <c r="F52" s="3">
-        <v>4300</v>
-      </c>
       <c r="G52" s="3">
-        <v>3200</v>
+        <v>4400</v>
       </c>
       <c r="H52" s="3">
-        <v>3000</v>
+        <v>3300</v>
       </c>
       <c r="I52" s="3">
-        <v>3500</v>
+        <v>3100</v>
       </c>
       <c r="J52" s="3">
+        <v>3600</v>
+      </c>
+      <c r="K52" s="3">
         <v>1400</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>12</v>
       </c>
@@ -2492,8 +2612,11 @@
       <c r="P52" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,35 +2659,38 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>205500</v>
+        <v>201000</v>
       </c>
       <c r="E54" s="3">
-        <v>186400</v>
+        <v>209700</v>
       </c>
       <c r="F54" s="3">
-        <v>171400</v>
+        <v>190200</v>
       </c>
       <c r="G54" s="3">
-        <v>169000</v>
+        <v>174900</v>
       </c>
       <c r="H54" s="3">
-        <v>156300</v>
+        <v>172500</v>
       </c>
       <c r="I54" s="3">
-        <v>116500</v>
+        <v>159500</v>
       </c>
       <c r="J54" s="3">
+        <v>118900</v>
+      </c>
+      <c r="K54" s="3">
         <v>89000</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>12</v>
       </c>
@@ -2580,8 +2706,11 @@
       <c r="P54" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2727,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,35 +2746,36 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>12000</v>
+        <v>8800</v>
       </c>
       <c r="E57" s="3">
-        <v>9300</v>
+        <v>12300</v>
       </c>
       <c r="F57" s="3">
-        <v>11100</v>
+        <v>9500</v>
       </c>
       <c r="G57" s="3">
-        <v>8600</v>
+        <v>11300</v>
       </c>
       <c r="H57" s="3">
-        <v>10400</v>
+        <v>8800</v>
       </c>
       <c r="I57" s="3">
-        <v>9800</v>
+        <v>10600</v>
       </c>
       <c r="J57" s="3">
+        <v>10000</v>
+      </c>
+      <c r="K57" s="3">
         <v>9600</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>12</v>
       </c>
@@ -2660,8 +2791,11 @@
       <c r="P57" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2704,35 +2838,38 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>138600</v>
+        <v>113800</v>
       </c>
       <c r="E59" s="3">
-        <v>121500</v>
+        <v>141400</v>
       </c>
       <c r="F59" s="3">
-        <v>116600</v>
+        <v>123900</v>
       </c>
       <c r="G59" s="3">
-        <v>121900</v>
+        <v>119000</v>
       </c>
       <c r="H59" s="3">
-        <v>120700</v>
+        <v>124400</v>
       </c>
       <c r="I59" s="3">
-        <v>117400</v>
+        <v>123100</v>
       </c>
       <c r="J59" s="3">
+        <v>119800</v>
+      </c>
+      <c r="K59" s="3">
         <v>102200</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>12</v>
       </c>
@@ -2748,35 +2885,38 @@
       <c r="P59" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>150600</v>
+        <v>122600</v>
       </c>
       <c r="E60" s="3">
-        <v>130800</v>
+        <v>153700</v>
       </c>
       <c r="F60" s="3">
-        <v>127700</v>
+        <v>133500</v>
       </c>
       <c r="G60" s="3">
-        <v>130500</v>
+        <v>130300</v>
       </c>
       <c r="H60" s="3">
-        <v>131100</v>
+        <v>133200</v>
       </c>
       <c r="I60" s="3">
-        <v>127200</v>
+        <v>133700</v>
       </c>
       <c r="J60" s="3">
+        <v>129800</v>
+      </c>
+      <c r="K60" s="3">
         <v>111800</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>12</v>
       </c>
@@ -2792,8 +2932,11 @@
       <c r="P60" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2836,35 +2979,38 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E62" s="3">
         <v>4100</v>
       </c>
-      <c r="E62" s="3">
-        <v>5800</v>
-      </c>
       <c r="F62" s="3">
-        <v>6900</v>
+        <v>5900</v>
       </c>
       <c r="G62" s="3">
-        <v>7300</v>
+        <v>7100</v>
       </c>
       <c r="H62" s="3">
-        <v>9000</v>
+        <v>7500</v>
       </c>
       <c r="I62" s="3">
-        <v>10400</v>
+        <v>9200</v>
       </c>
       <c r="J62" s="3">
+        <v>10600</v>
+      </c>
+      <c r="K62" s="3">
         <v>1200</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>12</v>
       </c>
@@ -2880,8 +3026,11 @@
       <c r="P62" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3073,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3120,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,35 +3167,38 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>154700</v>
+        <v>128200</v>
       </c>
       <c r="E66" s="3">
-        <v>136600</v>
+        <v>157800</v>
       </c>
       <c r="F66" s="3">
-        <v>134600</v>
+        <v>139400</v>
       </c>
       <c r="G66" s="3">
-        <v>138100</v>
+        <v>137300</v>
       </c>
       <c r="H66" s="3">
-        <v>140100</v>
+        <v>140900</v>
       </c>
       <c r="I66" s="3">
-        <v>137600</v>
+        <v>143000</v>
       </c>
       <c r="J66" s="3">
+        <v>140400</v>
+      </c>
+      <c r="K66" s="3">
         <v>113000</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>12</v>
       </c>
@@ -3056,8 +3214,11 @@
       <c r="P66" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3235,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3280,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3327,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3183,14 +3351,14 @@
         <v>0</v>
       </c>
       <c r="I70" s="3">
-        <v>94500</v>
+        <v>0</v>
       </c>
       <c r="J70" s="3">
+        <v>96400</v>
+      </c>
+      <c r="K70" s="3">
         <v>93100</v>
       </c>
-      <c r="K70" s="3">
-        <v>0</v>
-      </c>
       <c r="L70" s="3">
         <v>0</v>
       </c>
@@ -3206,8 +3374,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,35 +3421,38 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-107900</v>
+        <v>-82400</v>
       </c>
       <c r="E72" s="3">
-        <v>-109900</v>
+        <v>-110100</v>
       </c>
       <c r="F72" s="3">
-        <v>-124800</v>
+        <v>-112100</v>
       </c>
       <c r="G72" s="3">
-        <v>-134000</v>
+        <v>-127300</v>
       </c>
       <c r="H72" s="3">
-        <v>-141300</v>
+        <v>-136700</v>
       </c>
       <c r="I72" s="3">
-        <v>-138100</v>
+        <v>-144200</v>
       </c>
       <c r="J72" s="3">
+        <v>-141000</v>
+      </c>
+      <c r="K72" s="3">
         <v>-132400</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>12</v>
       </c>
@@ -3294,8 +3468,11 @@
       <c r="P72" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3515,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3562,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,35 +3609,38 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>50900</v>
+        <v>72800</v>
       </c>
       <c r="E76" s="3">
-        <v>49800</v>
+        <v>51900</v>
       </c>
       <c r="F76" s="3">
-        <v>36800</v>
+        <v>50800</v>
       </c>
       <c r="G76" s="3">
-        <v>30900</v>
+        <v>37600</v>
       </c>
       <c r="H76" s="3">
-        <v>16200</v>
+        <v>31500</v>
       </c>
       <c r="I76" s="3">
-        <v>-115600</v>
+        <v>16600</v>
       </c>
       <c r="J76" s="3">
+        <v>-118000</v>
+      </c>
+      <c r="K76" s="3">
         <v>-117100</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>12</v>
       </c>
@@ -3470,8 +3656,11 @@
       <c r="P76" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,101 +3703,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>2000</v>
+        <v>27700</v>
       </c>
       <c r="E81" s="3">
-        <v>14900</v>
+        <v>2100</v>
       </c>
       <c r="F81" s="3">
-        <v>9200</v>
+        <v>15200</v>
       </c>
       <c r="G81" s="3">
-        <v>7300</v>
+        <v>9400</v>
       </c>
       <c r="H81" s="3">
-        <v>-3500</v>
+        <v>7400</v>
       </c>
       <c r="I81" s="3">
-        <v>-7100</v>
+        <v>-3600</v>
       </c>
       <c r="J81" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="K81" s="3">
         <v>-14700</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M81" s="3">
         <v>-800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-7900</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,31 +3823,32 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>12</v>
+      <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
+        <v>0</v>
       </c>
       <c r="G83" s="3">
-        <v>500</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
+        <v>0</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>12</v>
@@ -3669,8 +3868,11 @@
       <c r="P83" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +3915,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +3962,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4009,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4056,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,31 +4103,34 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>12</v>
+      <c r="D89" s="3">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3">
+        <v>0</v>
       </c>
       <c r="G89" s="3">
-        <v>32600</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
+      </c>
+      <c r="H89" s="3">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
+        <v>0</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>12</v>
@@ -3933,8 +4150,11 @@
       <c r="P89" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,8 +4171,9 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3992,11 +4213,14 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4263,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,31 +4310,34 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>12</v>
+      <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
       </c>
       <c r="G94" s="3">
         <v>0</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>12</v>
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>12</v>
@@ -4127,8 +4357,11 @@
       <c r="P94" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,8 +4378,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4189,8 +4423,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4470,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4517,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,37 +4564,40 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>12</v>
+      <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
       </c>
       <c r="G100" s="3">
-        <v>34200</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
@@ -4359,37 +4605,40 @@
       <c r="N100" s="3">
         <v>0</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>12</v>
+      <c r="O100" s="3">
+        <v>0</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>12</v>
+      <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0</v>
       </c>
       <c r="G101" s="3">
-        <v>2000</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
+        <v>0</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>12</v>
@@ -4409,31 +4658,34 @@
       <c r="P101" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>12</v>
+      <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
       </c>
       <c r="G102" s="3">
-        <v>68800</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>12</v>
@@ -4451,6 +4703,9 @@
         <v>12</v>
       </c>
       <c r="P102" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>12</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/QSG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QSG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="92">
   <si>
     <t>QSG</t>
   </si>
@@ -656,225 +656,238 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>141000</v>
+        <v>115500</v>
       </c>
       <c r="E8" s="3">
-        <v>133300</v>
+        <v>137600</v>
       </c>
       <c r="F8" s="3">
-        <v>138200</v>
+        <v>131000</v>
       </c>
       <c r="G8" s="3">
-        <v>122500</v>
+        <v>138300</v>
       </c>
       <c r="H8" s="3">
-        <v>116800</v>
+        <v>119100</v>
       </c>
       <c r="I8" s="3">
-        <v>113800</v>
+        <v>114200</v>
       </c>
       <c r="J8" s="3">
+        <v>117500</v>
+      </c>
+      <c r="K8" s="3">
         <v>110900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>91100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>87400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>95400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>111000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>102500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>86000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>81200</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>19900</v>
+        <v>19200</v>
       </c>
       <c r="E9" s="3">
-        <v>20600</v>
+        <v>19400</v>
       </c>
       <c r="F9" s="3">
-        <v>20400</v>
+        <v>20200</v>
       </c>
       <c r="G9" s="3">
-        <v>16700</v>
+        <v>20500</v>
       </c>
       <c r="H9" s="3">
-        <v>16400</v>
+        <v>16200</v>
       </c>
       <c r="I9" s="3">
-        <v>14200</v>
+        <v>16000</v>
       </c>
       <c r="J9" s="3">
+        <v>14700</v>
+      </c>
+      <c r="K9" s="3">
         <v>14000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>10400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>15000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>31600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>27900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>11900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>7600</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>121100</v>
+        <v>96400</v>
       </c>
       <c r="E10" s="3">
-        <v>112700</v>
+        <v>118200</v>
       </c>
       <c r="F10" s="3">
+        <v>110800</v>
+      </c>
+      <c r="G10" s="3">
         <v>117800</v>
       </c>
-      <c r="G10" s="3">
-        <v>105900</v>
-      </c>
       <c r="H10" s="3">
-        <v>100400</v>
+        <v>102900</v>
       </c>
       <c r="I10" s="3">
-        <v>99600</v>
+        <v>98200</v>
       </c>
       <c r="J10" s="3">
+        <v>102800</v>
+      </c>
+      <c r="K10" s="3">
         <v>96900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>80700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>72500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>63800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>83200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>90600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>75600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>73600</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -892,55 +905,59 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="E12" s="3">
-        <v>5500</v>
+        <v>2900</v>
       </c>
       <c r="F12" s="3">
+        <v>5400</v>
+      </c>
+      <c r="G12" s="3">
         <v>5800</v>
       </c>
-      <c r="G12" s="3">
-        <v>6200</v>
-      </c>
       <c r="H12" s="3">
-        <v>7600</v>
+        <v>6000</v>
       </c>
       <c r="I12" s="3">
-        <v>7000</v>
+        <v>7400</v>
       </c>
       <c r="J12" s="3">
+        <v>7200</v>
+      </c>
+      <c r="K12" s="3">
         <v>9100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>7200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>18400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>13100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>14200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>10700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -986,16 +1003,19 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>1400</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>12</v>
+      <c r="D14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-1200</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>12</v>
@@ -1006,14 +1026,14 @@
       <c r="H14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>12</v>
+      <c r="I14" s="3">
+        <v>-1300</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1033,31 +1053,34 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1080,8 +1103,11 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,102 +1122,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>101000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>103800</v>
+      </c>
+      <c r="F17" s="3">
+        <v>131700</v>
+      </c>
+      <c r="G17" s="3">
+        <v>123800</v>
+      </c>
+      <c r="H17" s="3">
+        <v>113100</v>
+      </c>
+      <c r="I17" s="3">
         <v>107700</v>
       </c>
-      <c r="E17" s="3">
-        <v>134000</v>
-      </c>
-      <c r="F17" s="3">
-        <v>123800</v>
-      </c>
-      <c r="G17" s="3">
-        <v>116300</v>
-      </c>
-      <c r="H17" s="3">
-        <v>110100</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
+        <v>120900</v>
+      </c>
+      <c r="K17" s="3">
         <v>117100</v>
       </c>
-      <c r="J17" s="3">
-        <v>117100</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>104000</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N17" s="3">
         <v>95200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>103700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>114200</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>33300</v>
+        <v>14600</v>
       </c>
       <c r="E18" s="3">
+        <v>33800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>14400</v>
       </c>
-      <c r="G18" s="3">
-        <v>6200</v>
-      </c>
       <c r="H18" s="3">
-        <v>6700</v>
+        <v>6100</v>
       </c>
       <c r="I18" s="3">
-        <v>-3300</v>
+        <v>6600</v>
       </c>
       <c r="J18" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="K18" s="3">
         <v>-6300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-12900</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N18" s="3">
         <v>200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>7300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-11700</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1209,125 +1242,132 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1300</v>
+        <v>-1400</v>
       </c>
       <c r="E20" s="3">
-        <v>1400</v>
+        <v>1600</v>
       </c>
       <c r="F20" s="3">
-        <v>700</v>
+        <v>-1100</v>
       </c>
       <c r="G20" s="3">
-        <v>2200</v>
+        <v>-300</v>
       </c>
       <c r="H20" s="3">
-        <v>1300</v>
+        <v>-1700</v>
       </c>
       <c r="I20" s="3">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="J20" s="3">
+        <v>-800</v>
+      </c>
+      <c r="K20" s="3">
         <v>600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>900</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N20" s="3">
         <v>900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>800</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>12</v>
+      <c r="D21" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>32400</v>
+      </c>
+      <c r="F21" s="3">
+        <v>500</v>
+      </c>
+      <c r="G21" s="3">
+        <v>14900</v>
       </c>
       <c r="H21" s="3">
-        <v>8500</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K21" s="3">
+        <v>7900</v>
+      </c>
+      <c r="I21" s="3">
+        <v>6300</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L21" s="3">
         <v>-11900</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>12</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P21" s="3">
         <v>-10300</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1350,102 +1390,111 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>34500</v>
+        <v>16200</v>
       </c>
       <c r="E23" s="3">
+        <v>33700</v>
+      </c>
+      <c r="F23" s="3">
         <v>700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>15100</v>
       </c>
-      <c r="G23" s="3">
-        <v>8400</v>
-      </c>
       <c r="H23" s="3">
-        <v>7900</v>
+        <v>8200</v>
       </c>
       <c r="I23" s="3">
+        <v>7800</v>
+      </c>
+      <c r="J23" s="3">
         <v>-2300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-5700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-12000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-27700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-10800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-36700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>6800</v>
+        <v>4700</v>
       </c>
       <c r="E24" s="3">
+        <v>6600</v>
+      </c>
+      <c r="F24" s="3">
         <v>-1300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-100</v>
       </c>
-      <c r="G24" s="3">
-        <v>-1000</v>
-      </c>
       <c r="H24" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I24" s="3">
         <v>500</v>
       </c>
-      <c r="I24" s="3">
-        <v>900</v>
-      </c>
       <c r="J24" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-100</v>
-      </c>
-      <c r="P24" s="3">
-        <v>100</v>
       </c>
       <c r="Q24" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1491,102 +1540,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>27700</v>
+        <v>11500</v>
       </c>
       <c r="E26" s="3">
-        <v>2100</v>
+        <v>27100</v>
       </c>
       <c r="F26" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G26" s="3">
         <v>15200</v>
       </c>
-      <c r="G26" s="3">
-        <v>9400</v>
-      </c>
       <c r="H26" s="3">
-        <v>7400</v>
+        <v>9100</v>
       </c>
       <c r="I26" s="3">
-        <v>-3200</v>
+        <v>7300</v>
       </c>
       <c r="J26" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="K26" s="3">
         <v>-5800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-13400</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M26" s="3">
-        <v>0</v>
+      <c r="M26" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="N26" s="3">
+        <v>0</v>
+      </c>
+      <c r="O26" s="3">
         <v>6400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-10700</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>27700</v>
+        <v>11500</v>
       </c>
       <c r="E27" s="3">
-        <v>2100</v>
+        <v>27100</v>
       </c>
       <c r="F27" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G27" s="3">
         <v>15200</v>
       </c>
-      <c r="G27" s="3">
-        <v>9400</v>
-      </c>
       <c r="H27" s="3">
-        <v>7400</v>
+        <v>9100</v>
       </c>
       <c r="I27" s="3">
-        <v>-3600</v>
+        <v>7300</v>
       </c>
       <c r="J27" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="K27" s="3">
         <v>-7300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-14700</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N27" s="3">
         <v>-800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-7900</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1632,8 +1690,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1679,8 +1740,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1726,8 +1790,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1773,102 +1840,111 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1300</v>
+        <v>1400</v>
       </c>
       <c r="E32" s="3">
-        <v>-1400</v>
+        <v>-1600</v>
       </c>
       <c r="F32" s="3">
-        <v>-700</v>
+        <v>1100</v>
       </c>
       <c r="G32" s="3">
-        <v>-2200</v>
+        <v>300</v>
       </c>
       <c r="H32" s="3">
-        <v>-1300</v>
+        <v>1700</v>
       </c>
       <c r="I32" s="3">
-        <v>-1000</v>
+        <v>-400</v>
       </c>
       <c r="J32" s="3">
+        <v>800</v>
+      </c>
+      <c r="K32" s="3">
         <v>-600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-900</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N32" s="3">
         <v>-900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-800</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>27700</v>
+        <v>11500</v>
       </c>
       <c r="E33" s="3">
-        <v>2100</v>
+        <v>27100</v>
       </c>
       <c r="F33" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G33" s="3">
         <v>15200</v>
       </c>
-      <c r="G33" s="3">
-        <v>9400</v>
-      </c>
       <c r="H33" s="3">
-        <v>7400</v>
+        <v>9100</v>
       </c>
       <c r="I33" s="3">
-        <v>-3600</v>
+        <v>7300</v>
       </c>
       <c r="J33" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="K33" s="3">
         <v>-7300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-14700</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N33" s="3">
         <v>-800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-7900</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1914,107 +1990,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>27700</v>
+        <v>11500</v>
       </c>
       <c r="E35" s="3">
-        <v>2100</v>
+        <v>27100</v>
       </c>
       <c r="F35" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G35" s="3">
         <v>15200</v>
       </c>
-      <c r="G35" s="3">
-        <v>9400</v>
-      </c>
       <c r="H35" s="3">
-        <v>7400</v>
+        <v>9100</v>
       </c>
       <c r="I35" s="3">
-        <v>-3600</v>
+        <v>7300</v>
       </c>
       <c r="J35" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="K35" s="3">
         <v>-7300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-14700</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N35" s="3">
         <v>-800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-7900</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2032,8 +2117,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2051,38 +2137,39 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>110000</v>
+        <v>146400</v>
       </c>
       <c r="E41" s="3">
-        <v>137000</v>
+        <v>107300</v>
       </c>
       <c r="F41" s="3">
+        <v>134600</v>
+      </c>
+      <c r="G41" s="3">
         <v>121700</v>
       </c>
-      <c r="G41" s="3">
-        <v>97500</v>
-      </c>
       <c r="H41" s="3">
-        <v>107700</v>
+        <v>94800</v>
       </c>
       <c r="I41" s="3">
-        <v>66800</v>
+        <v>105400</v>
       </c>
       <c r="J41" s="3">
+        <v>69000</v>
+      </c>
+      <c r="K41" s="3">
         <v>59000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>62200</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>12</v>
       </c>
@@ -2098,38 +2185,41 @@
       <c r="Q41" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>34700</v>
+        <v>23700</v>
       </c>
       <c r="E42" s="3">
-        <v>25100</v>
+        <v>34600</v>
       </c>
       <c r="F42" s="3">
-        <v>26500</v>
+        <v>24700</v>
       </c>
       <c r="G42" s="3">
         <v>26500</v>
       </c>
       <c r="H42" s="3">
+        <v>25800</v>
+      </c>
+      <c r="I42" s="3">
         <v>23400</v>
       </c>
-      <c r="I42" s="3">
-        <v>53100</v>
-      </c>
       <c r="J42" s="3">
+        <v>54800</v>
+      </c>
+      <c r="K42" s="3">
         <v>15100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>800</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>12</v>
       </c>
@@ -2145,38 +2235,41 @@
       <c r="Q42" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>26100</v>
+        <v>2500</v>
       </c>
       <c r="E43" s="3">
+        <v>25500</v>
+      </c>
+      <c r="F43" s="3">
         <v>4300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2700</v>
       </c>
-      <c r="G43" s="3">
-        <v>3800</v>
-      </c>
       <c r="H43" s="3">
-        <v>5800</v>
+        <v>3700</v>
       </c>
       <c r="I43" s="3">
-        <v>5000</v>
+        <v>8800</v>
       </c>
       <c r="J43" s="3">
+        <v>5200</v>
+      </c>
+      <c r="K43" s="3">
         <v>4600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5400</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>12</v>
       </c>
@@ -2192,28 +2285,31 @@
       <c r="Q43" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="E44" s="3">
         <v>1000</v>
       </c>
       <c r="F44" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G44" s="3">
         <v>2100</v>
       </c>
-      <c r="G44" s="3">
-        <v>3100</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>12</v>
+      <c r="H44" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I44" s="3">
+        <v>1900</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>12</v>
@@ -2224,8 +2320,8 @@
       <c r="L44" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2239,38 +2335,41 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>29900</v>
+      </c>
+      <c r="E45" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F45" s="3">
+        <v>25300</v>
+      </c>
+      <c r="G45" s="3">
+        <v>22100</v>
+      </c>
+      <c r="H45" s="3">
+        <v>25600</v>
+      </c>
+      <c r="I45" s="3">
+        <v>800</v>
+      </c>
+      <c r="J45" s="3">
+        <v>17900</v>
+      </c>
+      <c r="K45" s="3">
+        <v>21000</v>
+      </c>
+      <c r="L45" s="3">
         <v>15700</v>
       </c>
-      <c r="E45" s="3">
-        <v>25800</v>
-      </c>
-      <c r="F45" s="3">
-        <v>22100</v>
-      </c>
-      <c r="G45" s="3">
-        <v>26300</v>
-      </c>
-      <c r="H45" s="3">
-        <v>19300</v>
-      </c>
-      <c r="I45" s="3">
-        <v>17300</v>
-      </c>
-      <c r="J45" s="3">
-        <v>21000</v>
-      </c>
-      <c r="K45" s="3">
-        <v>15700</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>12</v>
       </c>
@@ -2286,38 +2385,41 @@
       <c r="Q45" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>187400</v>
+        <v>203600</v>
       </c>
       <c r="E46" s="3">
-        <v>193300</v>
+        <v>182900</v>
       </c>
       <c r="F46" s="3">
+        <v>189900</v>
+      </c>
+      <c r="G46" s="3">
         <v>175100</v>
       </c>
-      <c r="G46" s="3">
-        <v>157300</v>
-      </c>
       <c r="H46" s="3">
-        <v>156300</v>
+        <v>152900</v>
       </c>
       <c r="I46" s="3">
-        <v>142200</v>
+        <v>152900</v>
       </c>
       <c r="J46" s="3">
+        <v>146800</v>
+      </c>
+      <c r="K46" s="3">
         <v>99700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>84100</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>12</v>
       </c>
@@ -2333,16 +2435,19 @@
       <c r="Q46" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1300</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>12</v>
+        <v>1500</v>
+      </c>
+      <c r="E47" s="3">
+        <v>1200</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>12</v>
@@ -2359,8 +2464,8 @@
       <c r="J47" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2380,38 +2485,41 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>9200</v>
+        <v>7600</v>
       </c>
       <c r="E48" s="3">
-        <v>10100</v>
+        <v>9000</v>
       </c>
       <c r="F48" s="3">
-        <v>10600</v>
+        <v>9900</v>
       </c>
       <c r="G48" s="3">
-        <v>11800</v>
+        <v>10700</v>
       </c>
       <c r="H48" s="3">
-        <v>12900</v>
+        <v>11400</v>
       </c>
       <c r="I48" s="3">
-        <v>14300</v>
+        <v>12600</v>
       </c>
       <c r="J48" s="3">
+        <v>14800</v>
+      </c>
+      <c r="K48" s="3">
         <v>15600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3500</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>12</v>
       </c>
@@ -2427,40 +2535,43 @@
       <c r="Q48" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>12</v>
+      <c r="D49" s="3">
+        <v>0</v>
       </c>
       <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>1400</v>
-      </c>
-      <c r="F49" s="3">
-        <v>1500</v>
       </c>
       <c r="G49" s="3">
         <v>1500</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M49" s="3">
-        <v>0</v>
+      <c r="H49" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
@@ -2474,8 +2585,11 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2521,8 +2635,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2568,8 +2685,11 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2577,29 +2697,29 @@
         <v>3100</v>
       </c>
       <c r="E52" s="3">
-        <v>4900</v>
+        <v>2900</v>
       </c>
       <c r="F52" s="3">
         <v>3000</v>
       </c>
       <c r="G52" s="3">
-        <v>4400</v>
+        <v>2900</v>
       </c>
       <c r="H52" s="3">
-        <v>3300</v>
+        <v>2800</v>
       </c>
       <c r="I52" s="3">
-        <v>3100</v>
+        <v>2900</v>
       </c>
       <c r="J52" s="3">
+        <v>3200</v>
+      </c>
+      <c r="K52" s="3">
         <v>3600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1400</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>12</v>
       </c>
@@ -2615,8 +2735,11 @@
       <c r="Q52" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2662,38 +2785,41 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>201000</v>
+        <v>216200</v>
       </c>
       <c r="E54" s="3">
-        <v>209700</v>
+        <v>196200</v>
       </c>
       <c r="F54" s="3">
-        <v>190200</v>
+        <v>206000</v>
       </c>
       <c r="G54" s="3">
-        <v>174900</v>
+        <v>190300</v>
       </c>
       <c r="H54" s="3">
-        <v>172500</v>
+        <v>170000</v>
       </c>
       <c r="I54" s="3">
-        <v>159500</v>
+        <v>168700</v>
       </c>
       <c r="J54" s="3">
+        <v>164700</v>
+      </c>
+      <c r="K54" s="3">
         <v>118900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>89000</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>12</v>
       </c>
@@ -2709,8 +2835,11 @@
       <c r="Q54" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2728,8 +2857,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2747,38 +2877,39 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>8800</v>
+        <v>8700</v>
       </c>
       <c r="E57" s="3">
-        <v>12300</v>
+        <v>8500</v>
       </c>
       <c r="F57" s="3">
+        <v>12000</v>
+      </c>
+      <c r="G57" s="3">
         <v>9500</v>
       </c>
-      <c r="G57" s="3">
-        <v>11300</v>
-      </c>
       <c r="H57" s="3">
-        <v>8800</v>
+        <v>11000</v>
       </c>
       <c r="I57" s="3">
-        <v>10600</v>
+        <v>8600</v>
       </c>
       <c r="J57" s="3">
+        <v>11000</v>
+      </c>
+      <c r="K57" s="3">
         <v>10000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9600</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>12</v>
       </c>
@@ -2794,31 +2925,34 @@
       <c r="Q57" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>6800</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>4700</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>5700</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>4900</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2841,38 +2975,41 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>113800</v>
+        <v>79300</v>
       </c>
       <c r="E59" s="3">
-        <v>141400</v>
+        <v>81000</v>
       </c>
       <c r="F59" s="3">
-        <v>123900</v>
+        <v>101700</v>
       </c>
       <c r="G59" s="3">
-        <v>119000</v>
+        <v>89800</v>
       </c>
       <c r="H59" s="3">
-        <v>124400</v>
+        <v>86700</v>
       </c>
       <c r="I59" s="3">
-        <v>123100</v>
+        <v>92600</v>
       </c>
       <c r="J59" s="3">
+        <v>101900</v>
+      </c>
+      <c r="K59" s="3">
         <v>119800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>102200</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>12</v>
       </c>
@@ -2888,38 +3025,41 @@
       <c r="Q59" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>122600</v>
+        <v>124700</v>
       </c>
       <c r="E60" s="3">
-        <v>153700</v>
+        <v>119700</v>
       </c>
       <c r="F60" s="3">
+        <v>151000</v>
+      </c>
+      <c r="G60" s="3">
         <v>133500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
+        <v>126600</v>
+      </c>
+      <c r="I60" s="3">
         <v>130300</v>
       </c>
-      <c r="H60" s="3">
-        <v>133200</v>
-      </c>
-      <c r="I60" s="3">
-        <v>133700</v>
-      </c>
       <c r="J60" s="3">
+        <v>138100</v>
+      </c>
+      <c r="K60" s="3">
         <v>129800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>111800</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>12</v>
       </c>
@@ -2935,31 +3075,34 @@
       <c r="Q60" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>5900</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>6900</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>7300</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>9500</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2982,38 +3125,41 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>5600</v>
-      </c>
-      <c r="E62" s="3">
-        <v>4100</v>
-      </c>
-      <c r="F62" s="3">
-        <v>5900</v>
-      </c>
-      <c r="G62" s="3">
-        <v>7100</v>
-      </c>
-      <c r="H62" s="3">
-        <v>7500</v>
-      </c>
-      <c r="I62" s="3">
-        <v>9200</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K62" s="3">
         <v>10600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1200</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>12</v>
       </c>
@@ -3029,8 +3175,11 @@
       <c r="Q62" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3076,8 +3225,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3123,8 +3275,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3170,38 +3325,41 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>128200</v>
+        <v>130300</v>
       </c>
       <c r="E66" s="3">
-        <v>157800</v>
+        <v>125200</v>
       </c>
       <c r="F66" s="3">
+        <v>155000</v>
+      </c>
+      <c r="G66" s="3">
         <v>139400</v>
       </c>
-      <c r="G66" s="3">
-        <v>137300</v>
-      </c>
       <c r="H66" s="3">
-        <v>140900</v>
+        <v>133500</v>
       </c>
       <c r="I66" s="3">
-        <v>143000</v>
+        <v>137600</v>
       </c>
       <c r="J66" s="3">
+        <v>147600</v>
+      </c>
+      <c r="K66" s="3">
         <v>140400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>113000</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>12</v>
       </c>
@@ -3217,8 +3375,11 @@
       <c r="Q66" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3236,8 +3397,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3283,8 +3445,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3330,8 +3495,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3354,14 +3522,14 @@
         <v>0</v>
       </c>
       <c r="J70" s="3">
+        <v>0</v>
+      </c>
+      <c r="K70" s="3">
         <v>96400</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>93100</v>
       </c>
-      <c r="L70" s="3">
-        <v>0</v>
-      </c>
       <c r="M70" s="3">
         <v>0</v>
       </c>
@@ -3377,8 +3545,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3424,38 +3595,41 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-82400</v>
+        <v>-71800</v>
       </c>
       <c r="E72" s="3">
-        <v>-110100</v>
+        <v>-80400</v>
       </c>
       <c r="F72" s="3">
-        <v>-112100</v>
+        <v>-108100</v>
       </c>
       <c r="G72" s="3">
-        <v>-127300</v>
+        <v>-112200</v>
       </c>
       <c r="H72" s="3">
-        <v>-136700</v>
+        <v>-123800</v>
       </c>
       <c r="I72" s="3">
-        <v>-144200</v>
+        <v>-133700</v>
       </c>
       <c r="J72" s="3">
+        <v>-148900</v>
+      </c>
+      <c r="K72" s="3">
         <v>-141000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-132400</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>12</v>
       </c>
@@ -3471,8 +3645,11 @@
       <c r="Q72" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3518,8 +3695,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3565,8 +3745,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3612,38 +3795,41 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>72800</v>
+        <v>85900</v>
       </c>
       <c r="E76" s="3">
-        <v>51900</v>
+        <v>71100</v>
       </c>
       <c r="F76" s="3">
-        <v>50800</v>
+        <v>51000</v>
       </c>
       <c r="G76" s="3">
-        <v>37600</v>
+        <v>50900</v>
       </c>
       <c r="H76" s="3">
-        <v>31500</v>
+        <v>36600</v>
       </c>
       <c r="I76" s="3">
-        <v>16600</v>
+        <v>30800</v>
       </c>
       <c r="J76" s="3">
+        <v>17100</v>
+      </c>
+      <c r="K76" s="3">
         <v>-118000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-117100</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>12</v>
       </c>
@@ -3659,8 +3845,11 @@
       <c r="Q76" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3706,107 +3895,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>27700</v>
+        <v>11500</v>
       </c>
       <c r="E81" s="3">
-        <v>2100</v>
+        <v>27100</v>
       </c>
       <c r="F81" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G81" s="3">
         <v>15200</v>
       </c>
-      <c r="G81" s="3">
-        <v>9400</v>
-      </c>
       <c r="H81" s="3">
-        <v>7400</v>
+        <v>9100</v>
       </c>
       <c r="I81" s="3">
-        <v>-3600</v>
+        <v>7300</v>
       </c>
       <c r="J81" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="K81" s="3">
         <v>-7300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-14700</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N81" s="3">
         <v>-800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-7900</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3824,34 +4022,35 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>12</v>
+        <v>100</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K83" s="3">
+        <v>0</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>12</v>
@@ -3871,8 +4070,11 @@
       <c r="Q83" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3918,8 +4120,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3965,8 +4170,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4012,8 +4220,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4059,8 +4270,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4106,34 +4320,37 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>0</v>
-      </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>12</v>
+      <c r="D89" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K89" s="3">
+        <v>0</v>
       </c>
       <c r="L89" s="3" t="s">
         <v>12</v>
@@ -4153,8 +4370,11 @@
       <c r="Q89" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4172,31 +4392,32 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -4216,11 +4437,14 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4266,8 +4490,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4313,34 +4540,37 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>12</v>
+      <c r="D94" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>12</v>
@@ -4360,8 +4590,11 @@
       <c r="Q94" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4379,31 +4612,32 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4426,8 +4660,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4473,8 +4710,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4520,8 +4760,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4567,40 +4810,43 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>12</v>
+      <c r="D100" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K100" s="3">
+        <v>0</v>
       </c>
       <c r="L100" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
@@ -4608,40 +4854,43 @@
       <c r="O100" s="3">
         <v>0</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>12</v>
+      <c r="P100" s="3">
+        <v>0</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>12</v>
+        <v>300</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K101" s="3">
+        <v>0</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>12</v>
@@ -4661,8 +4910,11 @@
       <c r="Q101" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4687,8 +4939,8 @@
       <c r="J102" s="3">
         <v>0</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>12</v>
+      <c r="K102" s="3">
+        <v>0</v>
       </c>
       <c r="L102" s="3" t="s">
         <v>12</v>
@@ -4706,6 +4958,9 @@
         <v>12</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>12</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/QSG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QSG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="92">
   <si>
     <t>QSG</t>
   </si>
@@ -656,238 +656,250 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>99600</v>
+      </c>
+      <c r="E8" s="3">
         <v>115500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>137600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>131000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>138300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>119100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>114200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>117500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>110900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>91100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>87400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>95400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>111000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>102500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>86000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>81200</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E9" s="3">
         <v>19200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>19400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>20200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>20500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>16200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>16000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>14700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>14000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>15000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>31600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>27900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>11900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>7600</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>82800</v>
+      </c>
+      <c r="E10" s="3">
         <v>96400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>118200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>110800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>117800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>102900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>98200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>102800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>96900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>80700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>72500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>63800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>83200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>90600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>75600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>73600</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -906,58 +918,62 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E12" s="3">
         <v>4000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>5400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>5800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>6000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>7400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>7200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>9100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>7200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>18400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>13100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>14200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>10700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1006,37 +1022,40 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="3">
         <v>-1200</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>12</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J14" s="3">
         <v>-1300</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1056,8 +1075,11 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1068,7 +1090,7 @@
         <v>200</v>
       </c>
       <c r="F15" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G15" s="3">
         <v>100</v>
@@ -1080,11 +1102,11 @@
         <v>100</v>
       </c>
       <c r="J15" s="3">
+        <v>100</v>
+      </c>
+      <c r="K15" s="3">
         <v>400</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1106,8 +1128,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1123,108 +1148,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>80600</v>
+      </c>
+      <c r="E17" s="3">
         <v>101000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>103800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>131700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>123800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>113100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>107700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>120900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>117100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>104000</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N17" s="3">
+      <c r="N17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O17" s="3">
         <v>95200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>103700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>114200</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E18" s="3">
         <v>14600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>33800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>14400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>6100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>6600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-3400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-6300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-12900</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O18" s="3">
         <v>200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>7300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-11700</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1243,108 +1275,115 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>900</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O20" s="3">
         <v>900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>800</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E21" s="3">
         <v>16100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>32400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>14900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>7900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>6300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2200</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M21" s="3">
         <v>-11900</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>12</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-10300</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1369,8 +1408,8 @@
       <c r="J22" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1393,108 +1432,117 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E23" s="3">
         <v>16200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>33700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>15100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>8200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>7800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-12000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-27700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-10800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-36700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E24" s="3">
         <v>4700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-100</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>100</v>
       </c>
       <c r="R24" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1543,108 +1591,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E26" s="3">
         <v>11500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>27100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>15200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>9100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>7300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-13400</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N26" s="3">
-        <v>0</v>
+      <c r="N26" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="O26" s="3">
+        <v>0</v>
+      </c>
+      <c r="P26" s="3">
         <v>6400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-10700</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E27" s="3">
         <v>11500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>27100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>15200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>9100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>7300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-7300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-14700</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="N27" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O27" s="3">
         <v>-800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1693,8 +1750,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1743,8 +1803,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1793,8 +1856,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1843,108 +1909,117 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>900</v>
+      </c>
+      <c r="E32" s="3">
         <v>1400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-900</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O32" s="3">
         <v>-900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-800</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E33" s="3">
         <v>11500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>27100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>15200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>9100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>7300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-7300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-14700</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="N33" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O33" s="3">
         <v>-800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1993,113 +2068,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E35" s="3">
         <v>11500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>27100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>15200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>9100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>7300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-7300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-14700</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="N35" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O35" s="3">
         <v>-800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2118,8 +2202,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2138,41 +2223,42 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>150000</v>
+      </c>
+      <c r="E41" s="3">
         <v>146400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>107300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>134600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>121700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>94800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>105400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>69000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>59000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>62200</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>12</v>
       </c>
@@ -2188,41 +2274,44 @@
       <c r="R41" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E42" s="3">
         <v>23700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>34600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>24700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>26500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>25800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>23400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>54800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>15100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>800</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="N42" s="3" t="s">
         <v>12</v>
       </c>
@@ -2238,41 +2327,44 @@
       <c r="R42" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E43" s="3">
         <v>2500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>25500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5400</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>12</v>
       </c>
@@ -2288,32 +2380,35 @@
       <c r="R43" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E44" s="3">
         <v>1100</v>
-      </c>
-      <c r="E44" s="3">
-        <v>1000</v>
       </c>
       <c r="F44" s="3">
         <v>1000</v>
       </c>
       <c r="G44" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H44" s="3">
         <v>2100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1900</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>12</v>
       </c>
@@ -2323,8 +2418,8 @@
       <c r="M44" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
+      <c r="N44" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
@@ -2338,41 +2433,44 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E45" s="3">
         <v>29900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>25300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>22100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>25600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>17900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>21000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>15700</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>12</v>
       </c>
@@ -2388,41 +2486,44 @@
       <c r="R45" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>191900</v>
+      </c>
+      <c r="E46" s="3">
         <v>203600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>182900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>189900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>175100</v>
-      </c>
-      <c r="H46" s="3">
-        <v>152900</v>
       </c>
       <c r="I46" s="3">
         <v>152900</v>
       </c>
       <c r="J46" s="3">
+        <v>152900</v>
+      </c>
+      <c r="K46" s="3">
         <v>146800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>99700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>84100</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>12</v>
       </c>
@@ -2438,20 +2539,23 @@
       <c r="R46" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E47" s="3">
         <v>1500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1200</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>12</v>
       </c>
@@ -2467,8 +2571,8 @@
       <c r="K47" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2488,41 +2592,44 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E48" s="3">
         <v>7600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>11400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>12600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>14800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>15600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3500</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>12</v>
       </c>
@@ -2538,8 +2645,11 @@
       <c r="R48" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2550,31 +2660,31 @@
         <v>0</v>
       </c>
       <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
         <v>1400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1400</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N49" s="3">
-        <v>0</v>
+      <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
@@ -2588,8 +2698,11 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2638,8 +2751,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2688,41 +2804,44 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>800</v>
+      </c>
+      <c r="E52" s="3">
         <v>3100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1400</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>12</v>
       </c>
@@ -2738,8 +2857,11 @@
       <c r="R52" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2788,41 +2910,44 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>203700</v>
+      </c>
+      <c r="E54" s="3">
         <v>216200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>196200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>206000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>190300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>170000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>168700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>164700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>118900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>89000</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>12</v>
       </c>
@@ -2838,8 +2963,11 @@
       <c r="R54" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2858,8 +2986,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2878,41 +3007,42 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E57" s="3">
         <v>8700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>12000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>9500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>11000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>11000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9600</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>12</v>
       </c>
@@ -2928,35 +3058,38 @@
       <c r="R57" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E58" s="3">
         <v>8000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4900</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -2978,41 +3111,44 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>65700</v>
+      </c>
+      <c r="E59" s="3">
         <v>79300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>81000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>101700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>89800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>86700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>92600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>101900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>119800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>102200</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>12</v>
       </c>
@@ -3028,41 +3164,44 @@
       <c r="R59" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>105300</v>
+      </c>
+      <c r="E60" s="3">
         <v>124700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>119700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>151000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>133500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>126600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>130300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>138100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>129800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>111800</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>12</v>
       </c>
@@ -3078,35 +3217,38 @@
       <c r="R60" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>300</v>
+      </c>
+      <c r="E61" s="3">
         <v>400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9500</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -3128,8 +3270,11 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3154,15 +3299,15 @@
       <c r="J62" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L62" s="3">
         <v>10600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1200</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>12</v>
       </c>
@@ -3178,8 +3323,11 @@
       <c r="R62" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3228,8 +3376,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3278,8 +3429,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3328,41 +3482,44 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>112800</v>
+      </c>
+      <c r="E66" s="3">
         <v>130300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>125200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>155000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>139400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>133500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>137600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>147600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>140400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>113000</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>12</v>
       </c>
@@ -3378,8 +3535,11 @@
       <c r="R66" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3398,8 +3558,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3448,8 +3609,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3498,8 +3662,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3525,14 +3692,14 @@
         <v>0</v>
       </c>
       <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3">
         <v>96400</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>93100</v>
       </c>
-      <c r="M70" s="3">
-        <v>0</v>
-      </c>
       <c r="N70" s="3">
         <v>0</v>
       </c>
@@ -3548,8 +3715,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3598,41 +3768,44 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-51600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-71800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-80400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-108100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-112200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-123800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-133700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-148900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-141000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-132400</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>12</v>
       </c>
@@ -3648,8 +3821,11 @@
       <c r="R72" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3698,8 +3874,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3748,8 +3927,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3798,41 +3980,44 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>90900</v>
+      </c>
+      <c r="E76" s="3">
         <v>85900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>71100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>51000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>50900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>36600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>30800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>17100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-118000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-117100</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>12</v>
       </c>
@@ -3848,8 +4033,11 @@
       <c r="R76" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3898,113 +4086,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E81" s="3">
         <v>11500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>27100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>15200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>9100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>7300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-7300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-14700</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="N81" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O81" s="3">
         <v>-800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4023,8 +4220,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4040,20 +4238,20 @@
       <c r="G83" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I83" s="3">
         <v>100</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="J83" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>12</v>
+      <c r="K83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L83" s="3">
+        <v>0</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>12</v>
@@ -4073,8 +4271,11 @@
       <c r="R83" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4123,8 +4324,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4173,8 +4377,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4223,8 +4430,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4273,8 +4483,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4323,8 +4536,11 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4349,11 +4565,11 @@
       <c r="J89" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>12</v>
+      <c r="K89" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L89" s="3">
+        <v>0</v>
       </c>
       <c r="M89" s="3" t="s">
         <v>12</v>
@@ -4373,8 +4589,11 @@
       <c r="R89" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4393,8 +4612,9 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4419,8 +4639,8 @@
       <c r="J91" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -4440,11 +4660,14 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4493,8 +4716,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4543,8 +4769,11 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4569,11 +4798,11 @@
       <c r="J94" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>12</v>
+      <c r="K94" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>12</v>
@@ -4593,8 +4822,11 @@
       <c r="R94" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4613,8 +4845,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4639,8 +4872,8 @@
       <c r="J96" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -4663,8 +4896,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4713,8 +4949,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4763,8 +5002,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4813,8 +5055,11 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4839,17 +5084,17 @@
       <c r="J100" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>12</v>
+      <c r="K100" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
+      <c r="N100" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="O100" s="3">
         <v>0</v>
@@ -4857,14 +5102,17 @@
       <c r="P100" s="3">
         <v>0</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>12</v>
+      <c r="Q100" s="3">
+        <v>0</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4880,20 +5128,20 @@
       <c r="G101" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H101" s="3">
+      <c r="H101" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I101" s="3">
         <v>300</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="J101" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>12</v>
+      <c r="K101" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>12</v>
@@ -4913,8 +5161,11 @@
       <c r="R101" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4942,8 +5193,8 @@
       <c r="K102" s="3">
         <v>0</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>12</v>
+      <c r="L102" s="3">
+        <v>0</v>
       </c>
       <c r="M102" s="3" t="s">
         <v>12</v>
@@ -4961,6 +5212,9 @@
         <v>12</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>12</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/QSG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QSG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="92">
   <si>
     <t>QSG</t>
   </si>
@@ -656,250 +656,263 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>99600</v>
-      </c>
-      <c r="E8" s="3">
+        <v>78600</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="3">
         <v>115500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>137600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>131000</v>
       </c>
-      <c r="H8" s="3">
-        <v>138300</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="I8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" s="3">
         <v>119100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>114200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>117500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>110900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>91100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>87400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>95400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>111000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>102500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>86000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>81200</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>16800</v>
-      </c>
-      <c r="E9" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="3">
         <v>19200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>19400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>20200</v>
       </c>
-      <c r="H9" s="3">
-        <v>20500</v>
-      </c>
-      <c r="I9" s="3">
+      <c r="I9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J9" s="3">
         <v>16200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>16000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>14700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>14000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>15000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>31600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>27900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>11900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>10500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>7600</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>82800</v>
-      </c>
-      <c r="E10" s="3">
+        <v>65300</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="3">
         <v>96400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>118200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>110800</v>
       </c>
-      <c r="H10" s="3">
-        <v>117800</v>
-      </c>
-      <c r="I10" s="3">
+      <c r="I10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J10" s="3">
         <v>102900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>98200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>102800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>96900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>80700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>72500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>63800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>83200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>90600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>75600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>73600</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -919,61 +932,65 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>3900</v>
-      </c>
-      <c r="E12" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="3">
         <v>4000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>5400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J12" s="3">
+        <v>6000</v>
+      </c>
+      <c r="K12" s="3">
+        <v>7400</v>
+      </c>
+      <c r="L12" s="3">
+        <v>7200</v>
+      </c>
+      <c r="M12" s="3">
+        <v>9100</v>
+      </c>
+      <c r="N12" s="3">
+        <v>7200</v>
+      </c>
+      <c r="O12" s="3">
+        <v>18400</v>
+      </c>
+      <c r="P12" s="3">
+        <v>13100</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>14200</v>
+      </c>
+      <c r="R12" s="3">
         <v>5800</v>
       </c>
-      <c r="I12" s="3">
-        <v>6000</v>
-      </c>
-      <c r="J12" s="3">
-        <v>7400</v>
-      </c>
-      <c r="K12" s="3">
-        <v>7200</v>
-      </c>
-      <c r="L12" s="3">
-        <v>9100</v>
-      </c>
-      <c r="M12" s="3">
-        <v>7200</v>
-      </c>
-      <c r="N12" s="3">
-        <v>18400</v>
-      </c>
-      <c r="O12" s="3">
-        <v>13100</v>
-      </c>
-      <c r="P12" s="3">
-        <v>14200</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>5800</v>
-      </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>10700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1025,8 +1042,11 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1036,29 +1056,29 @@
       <c r="E14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="3">
         <v>-1200</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K14" s="3">
         <v>-1300</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1078,8 +1098,11 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1087,29 +1110,29 @@
         <v>200</v>
       </c>
       <c r="E15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
         <v>200</v>
       </c>
       <c r="G15" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H15" s="3">
         <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
         <v>100</v>
       </c>
       <c r="K15" s="3">
+        <v>100</v>
+      </c>
+      <c r="L15" s="3">
         <v>400</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1131,8 +1154,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1149,114 +1175,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>80600</v>
-      </c>
-      <c r="E17" s="3">
+        <v>74100</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="3">
         <v>101000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>103800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>131700</v>
       </c>
-      <c r="H17" s="3">
-        <v>123800</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="I17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J17" s="3">
         <v>113100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>107700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>120900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>117100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>104000</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="O17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P17" s="3">
         <v>95200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>103700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>114200</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>18900</v>
-      </c>
-      <c r="E18" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="3">
         <v>14600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>33800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-700</v>
       </c>
-      <c r="H18" s="3">
-        <v>14400</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="I18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J18" s="3">
         <v>6100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>6600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-6300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-12900</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P18" s="3">
         <v>200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>7300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-11700</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1276,114 +1309,121 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-900</v>
-      </c>
-      <c r="E20" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="3">
         <v>-1400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1100</v>
       </c>
-      <c r="H20" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J20" s="3">
         <v>-1700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>900</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P20" s="3">
         <v>900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>800</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
         <v>16100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>32400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>500</v>
       </c>
-      <c r="H21" s="3">
-        <v>14900</v>
-      </c>
       <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
         <v>7900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>6300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2200</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N21" s="3">
         <v>-11900</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>12</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="R21" s="3">
         <v>-10300</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1411,8 +1451,8 @@
       <c r="K22" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1435,114 +1475,123 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>20000</v>
-      </c>
-      <c r="E23" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="3">
         <v>16200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>33700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>700</v>
       </c>
-      <c r="H23" s="3">
-        <v>15100</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="I23" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J23" s="3">
         <v>8200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>7800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-12000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-27700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>7600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-10800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-36700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>2600</v>
-      </c>
-      <c r="E24" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="3">
         <v>4700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J24" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K24" s="3">
+        <v>500</v>
+      </c>
+      <c r="L24" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M24" s="3">
+        <v>100</v>
+      </c>
+      <c r="N24" s="3">
+        <v>1400</v>
+      </c>
+      <c r="O24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P24" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="R24" s="3">
         <v>-100</v>
-      </c>
-      <c r="I24" s="3">
-        <v>-900</v>
-      </c>
-      <c r="J24" s="3">
-        <v>500</v>
-      </c>
-      <c r="K24" s="3">
-        <v>1000</v>
-      </c>
-      <c r="L24" s="3">
-        <v>100</v>
-      </c>
-      <c r="M24" s="3">
-        <v>1400</v>
-      </c>
-      <c r="N24" s="3">
-        <v>-300</v>
-      </c>
-      <c r="O24" s="3">
-        <v>1100</v>
-      </c>
-      <c r="P24" s="3">
-        <v>1200</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>-100</v>
-      </c>
-      <c r="R24" s="3">
-        <v>100</v>
       </c>
       <c r="S24" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1594,114 +1643,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>17400</v>
-      </c>
-      <c r="E26" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="3">
         <v>11500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>27100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2000</v>
       </c>
-      <c r="H26" s="3">
-        <v>15200</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="I26" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J26" s="3">
         <v>9100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>7300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-13400</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="O26" s="3">
-        <v>0</v>
+      <c r="O26" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="P26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="3">
         <v>6400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-10700</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>17400</v>
-      </c>
-      <c r="E27" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" s="3">
         <v>11500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>27100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2000</v>
       </c>
-      <c r="H27" s="3">
-        <v>15200</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="I27" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J27" s="3">
         <v>9100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>7300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-14700</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P27" s="3">
         <v>-800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-7900</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1753,8 +1811,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1806,8 +1867,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1859,8 +1923,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1912,114 +1979,123 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>900</v>
-      </c>
-      <c r="E32" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" s="3">
         <v>1400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1100</v>
       </c>
-      <c r="H32" s="3">
-        <v>300</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J32" s="3">
         <v>1700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-900</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P32" s="3">
         <v>-900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-800</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>17400</v>
-      </c>
-      <c r="E33" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" s="3">
         <v>11500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>27100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2000</v>
       </c>
-      <c r="H33" s="3">
-        <v>15200</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="I33" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J33" s="3">
         <v>9100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>7300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-14700</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P33" s="3">
         <v>-800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-7900</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2071,119 +2147,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>17400</v>
-      </c>
-      <c r="E35" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" s="3">
         <v>11500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>27100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2000</v>
       </c>
-      <c r="H35" s="3">
-        <v>15200</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="I35" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J35" s="3">
         <v>9100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>7300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-14700</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P35" s="3">
         <v>-800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-7900</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2203,8 +2288,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2224,44 +2310,45 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>150000</v>
-      </c>
-      <c r="E41" s="3">
+        <v>135800</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F41" s="3">
         <v>146400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>107300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>134600</v>
       </c>
-      <c r="H41" s="3">
-        <v>121700</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="I41" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J41" s="3">
         <v>94800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>105400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>69000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>59000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>62200</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>12</v>
       </c>
@@ -2277,44 +2364,47 @@
       <c r="S41" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>16100</v>
+        <v>20500</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>23700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>34600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>24700</v>
       </c>
-      <c r="H42" s="3">
-        <v>26500</v>
-      </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>25800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>23400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>54800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>15100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>800</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>12</v>
       </c>
@@ -2330,44 +2420,47 @@
       <c r="S42" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2200</v>
-      </c>
-      <c r="E43" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F43" s="3">
         <v>2500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>25500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4300</v>
       </c>
-      <c r="H43" s="3">
-        <v>2700</v>
-      </c>
-      <c r="I43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J43" s="3">
         <v>3700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5400</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>12</v>
       </c>
@@ -2383,35 +2476,38 @@
       <c r="S43" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1800</v>
-      </c>
-      <c r="E44" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F44" s="3">
         <v>1100</v>
-      </c>
-      <c r="F44" s="3">
-        <v>1000</v>
       </c>
       <c r="G44" s="3">
         <v>1000</v>
       </c>
       <c r="H44" s="3">
-        <v>2100</v>
-      </c>
-      <c r="I44" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J44" s="3">
         <v>3000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1900</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="L44" s="3" t="s">
         <v>12</v>
       </c>
@@ -2421,8 +2517,8 @@
       <c r="N44" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -2436,44 +2532,47 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>21600</v>
-      </c>
-      <c r="E45" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F45" s="3">
         <v>29900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>25300</v>
       </c>
-      <c r="H45" s="3">
-        <v>22100</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J45" s="3">
         <v>25600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>17900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>21000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>15700</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>12</v>
       </c>
@@ -2489,44 +2588,47 @@
       <c r="S45" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>191900</v>
-      </c>
-      <c r="E46" s="3">
+        <v>189400</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46" s="3">
         <v>203600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>182900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>189900</v>
       </c>
-      <c r="H46" s="3">
-        <v>175100</v>
-      </c>
-      <c r="I46" s="3">
-        <v>152900</v>
+      <c r="I46" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="J46" s="3">
         <v>152900</v>
       </c>
       <c r="K46" s="3">
+        <v>152900</v>
+      </c>
+      <c r="L46" s="3">
         <v>146800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>99700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>84100</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>12</v>
       </c>
@@ -2542,23 +2644,26 @@
       <c r="S46" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>4900</v>
-      </c>
-      <c r="E47" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F47" s="3">
         <v>1500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1200</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="H47" s="3" t="s">
         <v>12</v>
       </c>
@@ -2574,8 +2679,8 @@
       <c r="L47" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -2595,44 +2700,47 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5800</v>
-      </c>
-      <c r="E48" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F48" s="3">
         <v>7600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9900</v>
       </c>
-      <c r="H48" s="3">
-        <v>10700</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J48" s="3">
         <v>11400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>12600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>14800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>15600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3500</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>12</v>
       </c>
@@ -2648,46 +2756,49 @@
       <c r="S48" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
-      </c>
-      <c r="E49" s="3">
-        <v>0</v>
+        <v>35400</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="F49" s="3">
         <v>0</v>
       </c>
       <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
         <v>1400</v>
       </c>
-      <c r="H49" s="3">
-        <v>1500</v>
-      </c>
-      <c r="I49" s="3">
+      <c r="I49" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J49" s="3">
         <v>1400</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="O49" s="3">
-        <v>0</v>
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="P49" s="3">
         <v>0</v>
@@ -2701,8 +2812,11 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2754,8 +2868,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2807,44 +2924,47 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>800</v>
-      </c>
-      <c r="E52" s="3">
+        <v>700</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F52" s="3">
         <v>3100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J52" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K52" s="3">
         <v>2900</v>
       </c>
-      <c r="I52" s="3">
-        <v>2800</v>
-      </c>
-      <c r="J52" s="3">
-        <v>2900</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1400</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>12</v>
       </c>
@@ -2860,8 +2980,11 @@
       <c r="S52" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2913,44 +3036,47 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>203700</v>
-      </c>
-      <c r="E54" s="3">
+        <v>237400</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F54" s="3">
         <v>216200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>196200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>206000</v>
       </c>
-      <c r="H54" s="3">
-        <v>190300</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="I54" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J54" s="3">
         <v>170000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>168700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>164700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>118900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>89000</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>12</v>
       </c>
@@ -2966,8 +3092,11 @@
       <c r="S54" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2987,8 +3116,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3008,44 +3138,45 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>6300</v>
-      </c>
-      <c r="E57" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F57" s="3">
         <v>8700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>12000</v>
       </c>
-      <c r="H57" s="3">
-        <v>9500</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="I57" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J57" s="3">
         <v>11000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>9600</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>12</v>
       </c>
@@ -3061,38 +3192,41 @@
       <c r="S57" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
         <v>6200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="E58" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F58" s="3">
         <v>8000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6400</v>
       </c>
-      <c r="H58" s="3">
-        <v>5100</v>
-      </c>
-      <c r="I58" s="3">
+      <c r="I58" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J58" s="3">
         <v>4700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4900</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -3114,44 +3248,47 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>65700</v>
-      </c>
-      <c r="E59" s="3">
+        <v>70600</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F59" s="3">
         <v>79300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>81000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>101700</v>
       </c>
-      <c r="H59" s="3">
-        <v>89800</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J59" s="3">
         <v>86700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>92600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>101900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>119800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>102200</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>12</v>
       </c>
@@ -3167,44 +3304,47 @@
       <c r="S59" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>105300</v>
-      </c>
-      <c r="E60" s="3">
+        <v>110100</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F60" s="3">
         <v>124700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>119700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>151000</v>
       </c>
-      <c r="H60" s="3">
-        <v>133500</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="I60" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J60" s="3">
         <v>126600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>130300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>138100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>129800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>111800</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>12</v>
       </c>
@@ -3220,38 +3360,41 @@
       <c r="S60" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4100</v>
       </c>
-      <c r="H61" s="3">
-        <v>5900</v>
-      </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>6900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9500</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -3273,8 +3416,11 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3302,15 +3448,15 @@
       <c r="K62" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M62" s="3">
         <v>10600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1200</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>12</v>
       </c>
@@ -3326,8 +3472,11 @@
       <c r="S62" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3379,8 +3528,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3432,8 +3584,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3485,44 +3640,47 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>112800</v>
-      </c>
-      <c r="E66" s="3">
+        <v>120900</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F66" s="3">
         <v>130300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>125200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>155000</v>
       </c>
-      <c r="H66" s="3">
-        <v>139400</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="I66" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J66" s="3">
         <v>133500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>137600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>147600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>140400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>113000</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>12</v>
       </c>
@@ -3538,8 +3696,11 @@
       <c r="S66" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3559,8 +3720,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3612,8 +3774,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3665,8 +3830,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3695,14 +3863,14 @@
         <v>0</v>
       </c>
       <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
         <v>96400</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>93100</v>
       </c>
-      <c r="N70" s="3">
-        <v>0</v>
-      </c>
       <c r="O70" s="3">
         <v>0</v>
       </c>
@@ -3718,8 +3886,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3771,44 +3942,47 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-51600</v>
-      </c>
-      <c r="E72" s="3">
+        <v>-46200</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F72" s="3">
         <v>-71800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-80400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-108100</v>
       </c>
-      <c r="H72" s="3">
-        <v>-112200</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J72" s="3">
         <v>-123800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-133700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-148900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-141000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-132400</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>12</v>
       </c>
@@ -3824,8 +3998,11 @@
       <c r="S72" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3877,8 +4054,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3930,8 +4110,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3983,44 +4166,47 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>90900</v>
-      </c>
-      <c r="E76" s="3">
+        <v>97900</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F76" s="3">
         <v>85900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>71100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>51000</v>
       </c>
-      <c r="H76" s="3">
-        <v>50900</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="I76" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J76" s="3">
         <v>36600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>30800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>17100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-118000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-117100</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>12</v>
       </c>
@@ -4036,8 +4222,11 @@
       <c r="S76" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4089,119 +4278,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>17400</v>
-      </c>
-      <c r="E81" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F81" s="3">
         <v>11500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>27100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2000</v>
       </c>
-      <c r="H81" s="3">
-        <v>15200</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="I81" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J81" s="3">
         <v>9100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>7300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-14700</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P81" s="3">
         <v>-800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-7900</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4221,8 +4419,9 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4241,20 +4440,20 @@
       <c r="H83" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J83" s="3">
         <v>100</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="K83" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>12</v>
+      <c r="L83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>12</v>
@@ -4274,8 +4473,11 @@
       <c r="S83" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4327,8 +4529,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4380,8 +4585,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4433,8 +4641,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4486,8 +4697,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4539,8 +4753,11 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4568,11 +4785,11 @@
       <c r="K89" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>12</v>
+      <c r="L89" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M89" s="3">
+        <v>0</v>
       </c>
       <c r="N89" s="3" t="s">
         <v>12</v>
@@ -4592,8 +4809,11 @@
       <c r="S89" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4613,8 +4833,9 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4642,8 +4863,8 @@
       <c r="K91" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -4663,11 +4884,14 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4719,8 +4943,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4772,8 +4999,11 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4801,11 +5031,11 @@
       <c r="K94" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>12</v>
+      <c r="L94" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>12</v>
@@ -4825,8 +5055,11 @@
       <c r="S94" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4846,8 +5079,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4875,8 +5109,8 @@
       <c r="K96" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4899,8 +5133,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4952,8 +5189,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5005,8 +5245,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5058,8 +5301,11 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5087,17 +5333,17 @@
       <c r="K100" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>12</v>
+      <c r="L100" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
+      <c r="O100" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="P100" s="3">
         <v>0</v>
@@ -5105,14 +5351,17 @@
       <c r="Q100" s="3">
         <v>0</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>12</v>
+      <c r="R100" s="3">
+        <v>0</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5131,20 +5380,20 @@
       <c r="H101" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I101" s="3">
+      <c r="I101" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J101" s="3">
         <v>300</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="K101" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>12</v>
+      <c r="L101" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>12</v>
@@ -5164,8 +5413,11 @@
       <c r="S101" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5196,8 +5448,8 @@
       <c r="L102" s="3">
         <v>0</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>12</v>
+      <c r="M102" s="3">
+        <v>0</v>
       </c>
       <c r="N102" s="3" t="s">
         <v>12</v>
@@ -5215,6 +5467,9 @@
         <v>12</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>12</v>
       </c>
     </row>
